--- a/research/traditional_assets/database/data/romania/romania_electronics_general.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_electronics_general.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bvb_elma" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,43 +590,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.033</v>
+        <v>0.0181</v>
       </c>
       <c r="G2">
-        <v>0.006649937264742786</v>
+        <v>-0.04100580270793037</v>
       </c>
       <c r="H2">
-        <v>0.006649937264742786</v>
+        <v>-0.04100580270793037</v>
       </c>
       <c r="I2">
-        <v>-0.07578419071518193</v>
+        <v>0.07969052224371373</v>
       </c>
       <c r="J2">
-        <v>-0.07578419071518193</v>
+        <v>0.07924881958000723</v>
       </c>
       <c r="K2">
-        <v>-5.13</v>
+        <v>4.29</v>
       </c>
       <c r="L2">
-        <v>-0.064366373902133</v>
+        <v>0.08297872340425531</v>
       </c>
       <c r="M2">
-        <v>0.452</v>
+        <v>0.014</v>
       </c>
       <c r="N2">
-        <v>0.02916129032258065</v>
+        <v>0.0006572769953051643</v>
       </c>
       <c r="O2">
-        <v>-0.08810916179337232</v>
+        <v>0.003263403263403263</v>
       </c>
       <c r="P2">
-        <v>0.452</v>
+        <v>0.014</v>
       </c>
       <c r="Q2">
-        <v>0.02916129032258065</v>
+        <v>0.0006572769953051643</v>
       </c>
       <c r="R2">
-        <v>-0.08810916179337232</v>
+        <v>0.003263403263403263</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +635,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.736</v>
+        <v>1.27</v>
       </c>
       <c r="V2">
-        <v>0.04748387096774193</v>
+        <v>0.05962441314553991</v>
       </c>
       <c r="W2">
-        <v>-0.06380597014925372</v>
+        <v>0.05485933503836317</v>
       </c>
       <c r="X2">
-        <v>0.09639598016778718</v>
+        <v>0.1645951160372984</v>
       </c>
       <c r="Y2">
-        <v>-0.1602019503170409</v>
+        <v>-0.1097357809989352</v>
       </c>
       <c r="Z2">
-        <v>1.063503289254213</v>
+        <v>0.6668730490416119</v>
       </c>
       <c r="AA2">
-        <v>-0.08059673609906459</v>
+        <v>0.05284890194626802</v>
       </c>
       <c r="AB2">
-        <v>0.09615274416244121</v>
+        <v>0.1643842816199967</v>
       </c>
       <c r="AC2">
-        <v>-0.1767494802615058</v>
+        <v>-0.1115353796737286</v>
       </c>
       <c r="AD2">
-        <v>0.062</v>
+        <v>0.044</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.062</v>
+        <v>0.044</v>
       </c>
       <c r="AG2">
-        <v>-0.6739999999999999</v>
+        <v>-1.226</v>
       </c>
       <c r="AH2">
-        <v>0.00398406374501992</v>
+        <v>0.002061469265367316</v>
       </c>
       <c r="AI2">
-        <v>0.0007922107791776341</v>
+        <v>0.0005376081325448414</v>
       </c>
       <c r="AJ2">
-        <v>-0.04546067718872251</v>
+        <v>-0.06107402610341735</v>
       </c>
       <c r="AK2">
-        <v>-0.008693857544565694</v>
+        <v>-0.01521582644525529</v>
       </c>
       <c r="AL2">
-        <v>0.033</v>
+        <v>0.167</v>
       </c>
       <c r="AM2">
-        <v>-0.011</v>
+        <v>0.163</v>
       </c>
       <c r="AN2">
-        <v>-0.01405895691609977</v>
+        <v>0.007260726072607261</v>
       </c>
       <c r="AO2">
-        <v>-183.030303030303</v>
+        <v>24.67065868263473</v>
       </c>
       <c r="AP2">
-        <v>0.1528344671201814</v>
+        <v>-0.2023102310231023</v>
       </c>
       <c r="AQ2">
-        <v>549.0909090909093</v>
+        <v>25.2760736196319</v>
       </c>
     </row>
     <row r="3">
@@ -719,43 +721,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.033</v>
+        <v>0.0181</v>
       </c>
       <c r="G3">
-        <v>0.006649937264742786</v>
+        <v>-0.04100580270793037</v>
       </c>
       <c r="H3">
-        <v>0.006649937264742786</v>
+        <v>-0.04100580270793037</v>
       </c>
       <c r="I3">
-        <v>-0.07578419071518193</v>
+        <v>0.07969052224371373</v>
       </c>
       <c r="J3">
-        <v>-0.07578419071518193</v>
+        <v>0.07924881958000723</v>
       </c>
       <c r="K3">
-        <v>-5.13</v>
+        <v>4.29</v>
       </c>
       <c r="L3">
-        <v>-0.064366373902133</v>
+        <v>0.08297872340425531</v>
       </c>
       <c r="M3">
-        <v>0.452</v>
+        <v>0.014</v>
       </c>
       <c r="N3">
-        <v>0.02916129032258065</v>
+        <v>0.0006572769953051643</v>
       </c>
       <c r="O3">
-        <v>-0.08810916179337232</v>
+        <v>0.003263403263403263</v>
       </c>
       <c r="P3">
-        <v>0.452</v>
+        <v>0.014</v>
       </c>
       <c r="Q3">
-        <v>0.02916129032258065</v>
+        <v>0.0006572769953051643</v>
       </c>
       <c r="R3">
-        <v>-0.08810916179337232</v>
+        <v>0.003263403263403263</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +766,8785 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.736</v>
+        <v>1.27</v>
       </c>
       <c r="V3">
-        <v>0.04748387096774193</v>
+        <v>0.05962441314553991</v>
       </c>
       <c r="W3">
-        <v>-0.06380597014925372</v>
+        <v>0.05485933503836317</v>
       </c>
       <c r="X3">
-        <v>0.09639598016778718</v>
+        <v>0.1645951160372984</v>
       </c>
       <c r="Y3">
-        <v>-0.1602019503170409</v>
+        <v>-0.1097357809989352</v>
       </c>
       <c r="Z3">
-        <v>1.063503289254213</v>
+        <v>0.6668730490416119</v>
       </c>
       <c r="AA3">
-        <v>-0.08059673609906459</v>
+        <v>0.05284890194626802</v>
       </c>
       <c r="AB3">
-        <v>0.09615274416244121</v>
+        <v>0.1643842816199967</v>
       </c>
       <c r="AC3">
-        <v>-0.1767494802615058</v>
+        <v>-0.1115353796737286</v>
       </c>
       <c r="AD3">
-        <v>0.062</v>
+        <v>0.044</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.062</v>
+        <v>0.044</v>
       </c>
       <c r="AG3">
-        <v>-0.6739999999999999</v>
+        <v>-1.226</v>
       </c>
       <c r="AH3">
-        <v>0.00398406374501992</v>
+        <v>0.002061469265367316</v>
       </c>
       <c r="AI3">
-        <v>0.0007922107791776341</v>
+        <v>0.0005376081325448414</v>
       </c>
       <c r="AJ3">
-        <v>-0.04546067718872251</v>
+        <v>-0.06107402610341735</v>
       </c>
       <c r="AK3">
-        <v>-0.008693857544565694</v>
+        <v>-0.01521582644525529</v>
       </c>
       <c r="AL3">
-        <v>0.033</v>
+        <v>0.167</v>
       </c>
       <c r="AM3">
-        <v>-0.011</v>
+        <v>0.163</v>
       </c>
       <c r="AN3">
-        <v>-0.01405895691609977</v>
+        <v>0.007260726072607261</v>
       </c>
       <c r="AO3">
-        <v>-183.030303030303</v>
+        <v>24.67065868263473</v>
       </c>
       <c r="AP3">
-        <v>0.1528344671201814</v>
+        <v>-0.2023102310231023</v>
       </c>
       <c r="AQ3">
-        <v>549.0909090909093</v>
+        <v>25.2760736196319</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Electromagnetica S.A. (BVB:ELMA)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BVB:ELMA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Electronics (General)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.00206146926536732</v>
+      </c>
+      <c r="F2">
+        <v>0.79</v>
+      </c>
+      <c r="G2">
+        <v>21.3</v>
+      </c>
+      <c r="H2">
+        <v>5.33884745429674</v>
+      </c>
+      <c r="I2">
+        <v>20.074</v>
+      </c>
+      <c r="J2">
+        <v>20.9306074542967</v>
+      </c>
+      <c r="K2">
+        <v>0.044</v>
+      </c>
+      <c r="L2">
+        <v>16.86176</v>
+      </c>
+      <c r="M2">
+        <v>0.164384281619997</v>
+      </c>
+      <c r="N2">
+        <v>0.15435025331373</v>
+      </c>
+      <c r="O2">
+        <v>0.0623212568807339</v>
+      </c>
+      <c r="P2">
+        <v>0.0462</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.164595116037298</v>
+      </c>
+      <c r="T2">
+        <v>0.561201206255856</v>
+      </c>
+      <c r="U2">
+        <v>1.29582980760723</v>
+      </c>
+      <c r="V2">
+        <v>5.3813142824686</v>
+      </c>
+      <c r="W2">
+        <v>4.507240050860645</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>21.3</v>
+      </c>
+      <c r="AB2">
+        <v>0.09707688100614176</v>
+      </c>
+      <c r="AC2">
+        <v>0.07419197247706423</v>
+      </c>
+      <c r="AD2">
+        <v>0.16</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>6.06</v>
+      </c>
+      <c r="AH2">
+        <v>1.88</v>
+      </c>
+      <c r="AI2">
+        <v>0.03699999999999992</v>
+      </c>
+      <c r="AJ2">
+        <v>0.044</v>
+      </c>
+      <c r="AK2">
+        <v>0.044</v>
+      </c>
+      <c r="AL2">
+        <v>0.167</v>
+      </c>
+      <c r="AM2">
+        <v>0.044</v>
+      </c>
+      <c r="AN2">
+        <v>1.27</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.164377213042273</v>
+      </c>
+      <c r="C2">
+        <v>21.34457876621757</v>
+      </c>
+      <c r="D2">
+        <v>20.07457876621757</v>
+      </c>
+      <c r="E2">
+        <v>-0.044</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1.27</v>
+      </c>
+      <c r="H2">
+        <v>21.3</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>6.06</v>
+      </c>
+      <c r="K2">
+        <v>1.88</v>
+      </c>
+      <c r="L2">
+        <v>4.18</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>4.18</v>
+      </c>
+      <c r="O2">
+        <v>0.6688000000000001</v>
+      </c>
+      <c r="P2">
+        <v>3.5112</v>
+      </c>
+      <c r="Q2">
+        <v>5.3912</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.164377213042273</v>
+      </c>
+      <c r="T2">
+        <v>1.293585164054952</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.16</v>
+      </c>
+      <c r="W2">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1641721695014053</v>
+      </c>
+      <c r="C3">
+        <v>21.14794200969235</v>
+      </c>
+      <c r="D3">
+        <v>20.09138200969235</v>
+      </c>
+      <c r="E3">
+        <v>0.16944</v>
+      </c>
+      <c r="F3">
+        <v>0.21344</v>
+      </c>
+      <c r="G3">
+        <v>1.27</v>
+      </c>
+      <c r="H3">
+        <v>21.3</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>6.06</v>
+      </c>
+      <c r="K3">
+        <v>1.88</v>
+      </c>
+      <c r="L3">
+        <v>4.18</v>
+      </c>
+      <c r="M3">
+        <v>0.009754208000000002</v>
+      </c>
+      <c r="N3">
+        <v>4.170245791999999</v>
+      </c>
+      <c r="O3">
+        <v>0.66723932672</v>
+      </c>
+      <c r="P3">
+        <v>3.503006465279999</v>
+      </c>
+      <c r="Q3">
+        <v>5.383006465279999</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1654427166680862</v>
+      </c>
+      <c r="T3">
+        <v>1.304561038174206</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.16</v>
+      </c>
+      <c r="W3">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>428.532998271105</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1639671259605377</v>
+      </c>
+      <c r="C4">
+        <v>20.9513334067369</v>
+      </c>
+      <c r="D4">
+        <v>20.1082134067369</v>
+      </c>
+      <c r="E4">
+        <v>0.3828800000000001</v>
+      </c>
+      <c r="F4">
+        <v>0.42688</v>
+      </c>
+      <c r="G4">
+        <v>1.27</v>
+      </c>
+      <c r="H4">
+        <v>21.3</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>6.06</v>
+      </c>
+      <c r="K4">
+        <v>1.88</v>
+      </c>
+      <c r="L4">
+        <v>4.18</v>
+      </c>
+      <c r="M4">
+        <v>0.019508416</v>
+      </c>
+      <c r="N4">
+        <v>4.160491584</v>
+      </c>
+      <c r="O4">
+        <v>0.6656786534400001</v>
+      </c>
+      <c r="P4">
+        <v>3.49481293056</v>
+      </c>
+      <c r="Q4">
+        <v>5.374812930559999</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1665299652658548</v>
+      </c>
+      <c r="T4">
+        <v>1.315760909724466</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.16</v>
+      </c>
+      <c r="W4">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>214.2664991355525</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.16376208241967</v>
+      </c>
+      <c r="C5">
+        <v>20.75475302816684</v>
+      </c>
+      <c r="D5">
+        <v>20.12507302816684</v>
+      </c>
+      <c r="E5">
+        <v>0.59632</v>
+      </c>
+      <c r="F5">
+        <v>0.64032</v>
+      </c>
+      <c r="G5">
+        <v>1.27</v>
+      </c>
+      <c r="H5">
+        <v>21.3</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>6.06</v>
+      </c>
+      <c r="K5">
+        <v>1.88</v>
+      </c>
+      <c r="L5">
+        <v>4.18</v>
+      </c>
+      <c r="M5">
+        <v>0.029262624</v>
+      </c>
+      <c r="N5">
+        <v>4.150737375999999</v>
+      </c>
+      <c r="O5">
+        <v>0.66411798016</v>
+      </c>
+      <c r="P5">
+        <v>3.48661939584</v>
+      </c>
+      <c r="Q5">
+        <v>5.366619395839999</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1676396313604846</v>
+      </c>
+      <c r="T5">
+        <v>1.327191706461328</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.16</v>
+      </c>
+      <c r="W5">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>142.844332757035</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1635570388788024</v>
+      </c>
+      <c r="C6">
+        <v>20.55820094503548</v>
+      </c>
+      <c r="D6">
+        <v>20.14196094503549</v>
+      </c>
+      <c r="E6">
+        <v>0.80976</v>
+      </c>
+      <c r="F6">
+        <v>0.8537600000000001</v>
+      </c>
+      <c r="G6">
+        <v>1.27</v>
+      </c>
+      <c r="H6">
+        <v>21.3</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>6.06</v>
+      </c>
+      <c r="K6">
+        <v>1.88</v>
+      </c>
+      <c r="L6">
+        <v>4.18</v>
+      </c>
+      <c r="M6">
+        <v>0.03901683200000001</v>
+      </c>
+      <c r="N6">
+        <v>4.140983168</v>
+      </c>
+      <c r="O6">
+        <v>0.6625573068800001</v>
+      </c>
+      <c r="P6">
+        <v>3.47842586112</v>
+      </c>
+      <c r="Q6">
+        <v>5.35842586112</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1687724154987525</v>
+      </c>
+      <c r="T6">
+        <v>1.338860644796875</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.16</v>
+      </c>
+      <c r="W6">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>107.1332495677763</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1633519953379347</v>
+      </c>
+      <c r="C7">
+        <v>20.36167722863485</v>
+      </c>
+      <c r="D7">
+        <v>20.15887722863485</v>
+      </c>
+      <c r="E7">
+        <v>1.0232</v>
+      </c>
+      <c r="F7">
+        <v>1.0672</v>
+      </c>
+      <c r="G7">
+        <v>1.27</v>
+      </c>
+      <c r="H7">
+        <v>21.3</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>6.06</v>
+      </c>
+      <c r="K7">
+        <v>1.88</v>
+      </c>
+      <c r="L7">
+        <v>4.18</v>
+      </c>
+      <c r="M7">
+        <v>0.04877104000000001</v>
+      </c>
+      <c r="N7">
+        <v>4.13122896</v>
+      </c>
+      <c r="O7">
+        <v>0.6609966336</v>
+      </c>
+      <c r="P7">
+        <v>3.4702323264</v>
+      </c>
+      <c r="Q7">
+        <v>5.3502323264</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1699290477241419</v>
+      </c>
+      <c r="T7">
+        <v>1.350775244992118</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.16</v>
+      </c>
+      <c r="W7">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>85.70659965422101</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1631469517970671</v>
+      </c>
+      <c r="C8">
+        <v>20.16518195049665</v>
+      </c>
+      <c r="D8">
+        <v>20.17582195049664</v>
+      </c>
+      <c r="E8">
+        <v>1.23664</v>
+      </c>
+      <c r="F8">
+        <v>1.28064</v>
+      </c>
+      <c r="G8">
+        <v>1.27</v>
+      </c>
+      <c r="H8">
+        <v>21.3</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>6.06</v>
+      </c>
+      <c r="K8">
+        <v>1.88</v>
+      </c>
+      <c r="L8">
+        <v>4.18</v>
+      </c>
+      <c r="M8">
+        <v>0.05852524800000001</v>
+      </c>
+      <c r="N8">
+        <v>4.121474752</v>
+      </c>
+      <c r="O8">
+        <v>0.6594359603200002</v>
+      </c>
+      <c r="P8">
+        <v>3.46203879168</v>
+      </c>
+      <c r="Q8">
+        <v>5.34203879168</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1711102891458161</v>
+      </c>
+      <c r="T8">
+        <v>1.362943347319175</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.16</v>
+      </c>
+      <c r="W8">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>71.42216637851752</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1629419082561995</v>
+      </c>
+      <c r="C9">
+        <v>19.9687151823933</v>
+      </c>
+      <c r="D9">
+        <v>20.1927951823933</v>
+      </c>
+      <c r="E9">
+        <v>1.45008</v>
+      </c>
+      <c r="F9">
+        <v>1.49408</v>
+      </c>
+      <c r="G9">
+        <v>1.27</v>
+      </c>
+      <c r="H9">
+        <v>21.3</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>6.06</v>
+      </c>
+      <c r="K9">
+        <v>1.88</v>
+      </c>
+      <c r="L9">
+        <v>4.18</v>
+      </c>
+      <c r="M9">
+        <v>0.06827945600000002</v>
+      </c>
+      <c r="N9">
+        <v>4.111720544</v>
+      </c>
+      <c r="O9">
+        <v>0.6578752870400001</v>
+      </c>
+      <c r="P9">
+        <v>3.45384525696</v>
+      </c>
+      <c r="Q9">
+        <v>5.33384525696</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1723169336088167</v>
+      </c>
+      <c r="T9">
+        <v>1.375373129266168</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.16</v>
+      </c>
+      <c r="W9">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>61.21899975301501</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1627368647153319</v>
+      </c>
+      <c r="C10">
+        <v>19.77227699633897</v>
+      </c>
+      <c r="D10">
+        <v>20.20979699633897</v>
+      </c>
+      <c r="E10">
+        <v>1.66352</v>
+      </c>
+      <c r="F10">
+        <v>1.70752</v>
+      </c>
+      <c r="G10">
+        <v>1.27</v>
+      </c>
+      <c r="H10">
+        <v>21.3</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>6.06</v>
+      </c>
+      <c r="K10">
+        <v>1.88</v>
+      </c>
+      <c r="L10">
+        <v>4.18</v>
+      </c>
+      <c r="M10">
+        <v>0.07803366400000002</v>
+      </c>
+      <c r="N10">
+        <v>4.101966335999999</v>
+      </c>
+      <c r="O10">
+        <v>0.65631461376</v>
+      </c>
+      <c r="P10">
+        <v>3.445651722239999</v>
+      </c>
+      <c r="Q10">
+        <v>5.325651722239999</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1735498094731868</v>
+      </c>
+      <c r="T10">
+        <v>1.388073123864183</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.16</v>
+      </c>
+      <c r="W10">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>53.56662478388812</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1625318211744642</v>
+      </c>
+      <c r="C11">
+        <v>19.57586746459053</v>
+      </c>
+      <c r="D11">
+        <v>20.22682746459054</v>
+      </c>
+      <c r="E11">
+        <v>1.87696</v>
+      </c>
+      <c r="F11">
+        <v>1.92096</v>
+      </c>
+      <c r="G11">
+        <v>1.27</v>
+      </c>
+      <c r="H11">
+        <v>21.3</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>6.06</v>
+      </c>
+      <c r="K11">
+        <v>1.88</v>
+      </c>
+      <c r="L11">
+        <v>4.18</v>
+      </c>
+      <c r="M11">
+        <v>0.087787872</v>
+      </c>
+      <c r="N11">
+        <v>4.092212128</v>
+      </c>
+      <c r="O11">
+        <v>0.6547539404800001</v>
+      </c>
+      <c r="P11">
+        <v>3.43745818752</v>
+      </c>
+      <c r="Q11">
+        <v>5.31745818752</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1748097815104002</v>
+      </c>
+      <c r="T11">
+        <v>1.401052239222594</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.16</v>
+      </c>
+      <c r="W11">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>47.61477758567835</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1623267776335966</v>
+      </c>
+      <c r="C12">
+        <v>19.37948665964865</v>
+      </c>
+      <c r="D12">
+        <v>20.24388665964865</v>
+      </c>
+      <c r="E12">
+        <v>2.0904</v>
+      </c>
+      <c r="F12">
+        <v>2.1344</v>
+      </c>
+      <c r="G12">
+        <v>1.27</v>
+      </c>
+      <c r="H12">
+        <v>21.3</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>6.06</v>
+      </c>
+      <c r="K12">
+        <v>1.88</v>
+      </c>
+      <c r="L12">
+        <v>4.18</v>
+      </c>
+      <c r="M12">
+        <v>0.09754208000000002</v>
+      </c>
+      <c r="N12">
+        <v>4.08245792</v>
+      </c>
+      <c r="O12">
+        <v>0.6531932672</v>
+      </c>
+      <c r="P12">
+        <v>3.4292646528</v>
+      </c>
+      <c r="Q12">
+        <v>5.3092646528</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1760977529262184</v>
+      </c>
+      <c r="T12">
+        <v>1.414319779366747</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.16</v>
+      </c>
+      <c r="W12">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>42.8532998271105</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.162121734092729</v>
+      </c>
+      <c r="C13">
+        <v>19.18313465425875</v>
+      </c>
+      <c r="D13">
+        <v>20.26097465425875</v>
+      </c>
+      <c r="E13">
+        <v>2.30384</v>
+      </c>
+      <c r="F13">
+        <v>2.34784</v>
+      </c>
+      <c r="G13">
+        <v>1.27</v>
+      </c>
+      <c r="H13">
+        <v>21.3</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>6.06</v>
+      </c>
+      <c r="K13">
+        <v>1.88</v>
+      </c>
+      <c r="L13">
+        <v>4.18</v>
+      </c>
+      <c r="M13">
+        <v>0.107296288</v>
+      </c>
+      <c r="N13">
+        <v>4.072703712</v>
+      </c>
+      <c r="O13">
+        <v>0.6516325939200002</v>
+      </c>
+      <c r="P13">
+        <v>3.42107111808</v>
+      </c>
+      <c r="Q13">
+        <v>5.301071118079999</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1774146675199202</v>
+      </c>
+      <c r="T13">
+        <v>1.427885466480433</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.16</v>
+      </c>
+      <c r="W13">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>38.95754529737319</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1619166905518613</v>
+      </c>
+      <c r="C14">
+        <v>18.98681152141213</v>
+      </c>
+      <c r="D14">
+        <v>20.27809152141213</v>
+      </c>
+      <c r="E14">
+        <v>2.51728</v>
+      </c>
+      <c r="F14">
+        <v>2.56128</v>
+      </c>
+      <c r="G14">
+        <v>1.27</v>
+      </c>
+      <c r="H14">
+        <v>21.3</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>6.06</v>
+      </c>
+      <c r="K14">
+        <v>1.88</v>
+      </c>
+      <c r="L14">
+        <v>4.18</v>
+      </c>
+      <c r="M14">
+        <v>0.117050496</v>
+      </c>
+      <c r="N14">
+        <v>4.062949504</v>
+      </c>
+      <c r="O14">
+        <v>0.6500719206400001</v>
+      </c>
+      <c r="P14">
+        <v>3.412877583359999</v>
+      </c>
+      <c r="Q14">
+        <v>5.292877583359999</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1787615119907515</v>
+      </c>
+      <c r="T14">
+        <v>1.441759464664883</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.16</v>
+      </c>
+      <c r="W14">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>35.71108318925875</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1617116470109937</v>
+      </c>
+      <c r="C15">
+        <v>18.7905173343469</v>
+      </c>
+      <c r="D15">
+        <v>20.2952373343469</v>
+      </c>
+      <c r="E15">
+        <v>2.73072</v>
+      </c>
+      <c r="F15">
+        <v>2.77472</v>
+      </c>
+      <c r="G15">
+        <v>1.27</v>
+      </c>
+      <c r="H15">
+        <v>21.3</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>6.06</v>
+      </c>
+      <c r="K15">
+        <v>1.88</v>
+      </c>
+      <c r="L15">
+        <v>4.18</v>
+      </c>
+      <c r="M15">
+        <v>0.126804704</v>
+      </c>
+      <c r="N15">
+        <v>4.053195295999999</v>
+      </c>
+      <c r="O15">
+        <v>0.64851124736</v>
+      </c>
+      <c r="P15">
+        <v>3.404684048639999</v>
+      </c>
+      <c r="Q15">
+        <v>5.284684048639999</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.180139318403441</v>
+      </c>
+      <c r="T15">
+        <v>1.455952405336332</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.16</v>
+      </c>
+      <c r="W15">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>32.964076790085</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.161506603470126</v>
+      </c>
+      <c r="C16">
+        <v>18.59425216654914</v>
+      </c>
+      <c r="D16">
+        <v>20.31241216654914</v>
+      </c>
+      <c r="E16">
+        <v>2.944160000000001</v>
+      </c>
+      <c r="F16">
+        <v>2.988160000000001</v>
+      </c>
+      <c r="G16">
+        <v>1.27</v>
+      </c>
+      <c r="H16">
+        <v>21.3</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>6.06</v>
+      </c>
+      <c r="K16">
+        <v>1.88</v>
+      </c>
+      <c r="L16">
+        <v>4.18</v>
+      </c>
+      <c r="M16">
+        <v>0.136558912</v>
+      </c>
+      <c r="N16">
+        <v>4.043441088</v>
+      </c>
+      <c r="O16">
+        <v>0.6469505740800001</v>
+      </c>
+      <c r="P16">
+        <v>3.39649051392</v>
+      </c>
+      <c r="Q16">
+        <v>5.27649051392</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.181549166825728</v>
+      </c>
+      <c r="T16">
+        <v>1.47047541439549</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.16</v>
+      </c>
+      <c r="W16">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>30.6094998765075</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1613015599292584</v>
+      </c>
+      <c r="C17">
+        <v>18.39801609175383</v>
+      </c>
+      <c r="D17">
+        <v>20.32961609175383</v>
+      </c>
+      <c r="E17">
+        <v>3.1576</v>
+      </c>
+      <c r="F17">
+        <v>3.2016</v>
+      </c>
+      <c r="G17">
+        <v>1.27</v>
+      </c>
+      <c r="H17">
+        <v>21.3</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>6.06</v>
+      </c>
+      <c r="K17">
+        <v>1.88</v>
+      </c>
+      <c r="L17">
+        <v>4.18</v>
+      </c>
+      <c r="M17">
+        <v>0.14631312</v>
+      </c>
+      <c r="N17">
+        <v>4.033686879999999</v>
+      </c>
+      <c r="O17">
+        <v>0.6453899008</v>
+      </c>
+      <c r="P17">
+        <v>3.388296979199999</v>
+      </c>
+      <c r="Q17">
+        <v>5.268296979199999</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1829921881520687</v>
+      </c>
+      <c r="T17">
+        <v>1.485340141314863</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.16</v>
+      </c>
+      <c r="W17">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>28.568866551407</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1610965163883908</v>
+      </c>
+      <c r="C18">
+        <v>18.20180918394602</v>
+      </c>
+      <c r="D18">
+        <v>20.34684918394602</v>
+      </c>
+      <c r="E18">
+        <v>3.37104</v>
+      </c>
+      <c r="F18">
+        <v>3.41504</v>
+      </c>
+      <c r="G18">
+        <v>1.27</v>
+      </c>
+      <c r="H18">
+        <v>21.3</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>6.06</v>
+      </c>
+      <c r="K18">
+        <v>1.88</v>
+      </c>
+      <c r="L18">
+        <v>4.18</v>
+      </c>
+      <c r="M18">
+        <v>0.156067328</v>
+      </c>
+      <c r="N18">
+        <v>4.023932672</v>
+      </c>
+      <c r="O18">
+        <v>0.6438292275200002</v>
+      </c>
+      <c r="P18">
+        <v>3.38010344448</v>
+      </c>
+      <c r="Q18">
+        <v>5.260103444479999</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1844695671290366</v>
+      </c>
+      <c r="T18">
+        <v>1.500558790303744</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.16</v>
+      </c>
+      <c r="W18">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>26.78331239194407</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1608914728475231</v>
+      </c>
+      <c r="C19">
+        <v>18.0056315173618</v>
+      </c>
+      <c r="D19">
+        <v>20.3641115173618</v>
+      </c>
+      <c r="E19">
+        <v>3.584480000000001</v>
+      </c>
+      <c r="F19">
+        <v>3.628480000000001</v>
+      </c>
+      <c r="G19">
+        <v>1.27</v>
+      </c>
+      <c r="H19">
+        <v>21.3</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>6.06</v>
+      </c>
+      <c r="K19">
+        <v>1.88</v>
+      </c>
+      <c r="L19">
+        <v>4.18</v>
+      </c>
+      <c r="M19">
+        <v>0.165821536</v>
+      </c>
+      <c r="N19">
+        <v>4.014178464</v>
+      </c>
+      <c r="O19">
+        <v>0.6422685542400001</v>
+      </c>
+      <c r="P19">
+        <v>3.371909909759999</v>
+      </c>
+      <c r="Q19">
+        <v>5.251909909759999</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1859825455994255</v>
+      </c>
+      <c r="T19">
+        <v>1.516144153726093</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.16</v>
+      </c>
+      <c r="W19">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>25.20782342771206</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1606864293066555</v>
+      </c>
+      <c r="C20">
+        <v>17.80948316648942</v>
+      </c>
+      <c r="D20">
+        <v>20.38140316648942</v>
+      </c>
+      <c r="E20">
+        <v>3.79792</v>
+      </c>
+      <c r="F20">
+        <v>3.84192</v>
+      </c>
+      <c r="G20">
+        <v>1.27</v>
+      </c>
+      <c r="H20">
+        <v>21.3</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>6.06</v>
+      </c>
+      <c r="K20">
+        <v>1.88</v>
+      </c>
+      <c r="L20">
+        <v>4.18</v>
+      </c>
+      <c r="M20">
+        <v>0.175575744</v>
+      </c>
+      <c r="N20">
+        <v>4.004424256</v>
+      </c>
+      <c r="O20">
+        <v>0.6407078809600001</v>
+      </c>
+      <c r="P20">
+        <v>3.36371637504</v>
+      </c>
+      <c r="Q20">
+        <v>5.24371637504</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1875324259837262</v>
+      </c>
+      <c r="T20">
+        <v>1.532109647963621</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.16</v>
+      </c>
+      <c r="W20">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>23.80738879283917</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1604813857657879</v>
+      </c>
+      <c r="C21">
+        <v>17.61336420607034</v>
+      </c>
+      <c r="D21">
+        <v>20.39872420607034</v>
+      </c>
+      <c r="E21">
+        <v>4.011360000000001</v>
+      </c>
+      <c r="F21">
+        <v>4.05536</v>
+      </c>
+      <c r="G21">
+        <v>1.27</v>
+      </c>
+      <c r="H21">
+        <v>21.3</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>6.06</v>
+      </c>
+      <c r="K21">
+        <v>1.88</v>
+      </c>
+      <c r="L21">
+        <v>4.18</v>
+      </c>
+      <c r="M21">
+        <v>0.185329952</v>
+      </c>
+      <c r="N21">
+        <v>3.994670048</v>
+      </c>
+      <c r="O21">
+        <v>0.6391472076800001</v>
+      </c>
+      <c r="P21">
+        <v>3.355522840319999</v>
+      </c>
+      <c r="Q21">
+        <v>5.23552284032</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1891205750194911</v>
+      </c>
+      <c r="T21">
+        <v>1.548469351935409</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.16</v>
+      </c>
+      <c r="W21">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>22.55436833005816</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1602763422249202</v>
+      </c>
+      <c r="C22">
+        <v>17.4172747111003</v>
+      </c>
+      <c r="D22">
+        <v>20.41607471110031</v>
+      </c>
+      <c r="E22">
+        <v>4.224800000000001</v>
+      </c>
+      <c r="F22">
+        <v>4.268800000000001</v>
+      </c>
+      <c r="G22">
+        <v>1.27</v>
+      </c>
+      <c r="H22">
+        <v>21.3</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>6.06</v>
+      </c>
+      <c r="K22">
+        <v>1.88</v>
+      </c>
+      <c r="L22">
+        <v>4.18</v>
+      </c>
+      <c r="M22">
+        <v>0.19508416</v>
+      </c>
+      <c r="N22">
+        <v>3.98491584</v>
+      </c>
+      <c r="O22">
+        <v>0.6375865344000001</v>
+      </c>
+      <c r="P22">
+        <v>3.3473293056</v>
+      </c>
+      <c r="Q22">
+        <v>5.2273293056</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1907484277811503</v>
+      </c>
+      <c r="T22">
+        <v>1.565238048506492</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.16</v>
+      </c>
+      <c r="W22">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>21.42664991355525</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1600712986840526</v>
+      </c>
+      <c r="C23">
+        <v>17.22121475683044</v>
+      </c>
+      <c r="D23">
+        <v>20.43345475683044</v>
+      </c>
+      <c r="E23">
+        <v>4.43824</v>
+      </c>
+      <c r="F23">
+        <v>4.48224</v>
+      </c>
+      <c r="G23">
+        <v>1.27</v>
+      </c>
+      <c r="H23">
+        <v>21.3</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>6.06</v>
+      </c>
+      <c r="K23">
+        <v>1.88</v>
+      </c>
+      <c r="L23">
+        <v>4.18</v>
+      </c>
+      <c r="M23">
+        <v>0.204838368</v>
+      </c>
+      <c r="N23">
+        <v>3.975161632</v>
+      </c>
+      <c r="O23">
+        <v>0.6360258611200001</v>
+      </c>
+      <c r="P23">
+        <v>3.33913577088</v>
+      </c>
+      <c r="Q23">
+        <v>5.219135770879999</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1924174920051298</v>
+      </c>
+      <c r="T23">
+        <v>1.5824312690414</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.16</v>
+      </c>
+      <c r="W23">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>20.40633325100501</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1598662551431849</v>
+      </c>
+      <c r="C24">
+        <v>17.02518441876834</v>
+      </c>
+      <c r="D24">
+        <v>20.45086441876834</v>
+      </c>
+      <c r="E24">
+        <v>4.651680000000001</v>
+      </c>
+      <c r="F24">
+        <v>4.69568</v>
+      </c>
+      <c r="G24">
+        <v>1.27</v>
+      </c>
+      <c r="H24">
+        <v>21.3</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>6.06</v>
+      </c>
+      <c r="K24">
+        <v>1.88</v>
+      </c>
+      <c r="L24">
+        <v>4.18</v>
+      </c>
+      <c r="M24">
+        <v>0.214592576</v>
+      </c>
+      <c r="N24">
+        <v>3.965407423999999</v>
+      </c>
+      <c r="O24">
+        <v>0.6344651878400001</v>
+      </c>
+      <c r="P24">
+        <v>3.330942236159999</v>
+      </c>
+      <c r="Q24">
+        <v>5.210942236159999</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.194129352747673</v>
+      </c>
+      <c r="T24">
+        <v>1.600065341384894</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0.16</v>
+      </c>
+      <c r="W24">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>19.47877264868659</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1596612116023173</v>
+      </c>
+      <c r="C25">
+        <v>16.82918377267913</v>
+      </c>
+      <c r="D25">
+        <v>20.46830377267913</v>
+      </c>
+      <c r="E25">
+        <v>4.865120000000001</v>
+      </c>
+      <c r="F25">
+        <v>4.909120000000001</v>
+      </c>
+      <c r="G25">
+        <v>1.27</v>
+      </c>
+      <c r="H25">
+        <v>21.3</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>6.06</v>
+      </c>
+      <c r="K25">
+        <v>1.88</v>
+      </c>
+      <c r="L25">
+        <v>4.18</v>
+      </c>
+      <c r="M25">
+        <v>0.224346784</v>
+      </c>
+      <c r="N25">
+        <v>3.955653216</v>
+      </c>
+      <c r="O25">
+        <v>0.6329045145600001</v>
+      </c>
+      <c r="P25">
+        <v>3.322748701439999</v>
+      </c>
+      <c r="Q25">
+        <v>5.202748701439999</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1958856774056069</v>
+      </c>
+      <c r="T25">
+        <v>1.618157441581467</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0.16</v>
+      </c>
+      <c r="W25">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>18.63186949004804</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1594561680614497</v>
+      </c>
+      <c r="C26">
+        <v>16.6332128945866</v>
+      </c>
+      <c r="D26">
+        <v>20.4857728945866</v>
+      </c>
+      <c r="E26">
+        <v>5.07856</v>
+      </c>
+      <c r="F26">
+        <v>5.12256</v>
+      </c>
+      <c r="G26">
+        <v>1.27</v>
+      </c>
+      <c r="H26">
+        <v>21.3</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>6.06</v>
+      </c>
+      <c r="K26">
+        <v>1.88</v>
+      </c>
+      <c r="L26">
+        <v>4.18</v>
+      </c>
+      <c r="M26">
+        <v>0.234100992</v>
+      </c>
+      <c r="N26">
+        <v>3.945899008</v>
+      </c>
+      <c r="O26">
+        <v>0.6313438412800001</v>
+      </c>
+      <c r="P26">
+        <v>3.31455516672</v>
+      </c>
+      <c r="Q26">
+        <v>5.194555166719999</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1976882211334864</v>
+      </c>
+      <c r="T26">
+        <v>1.63672564967795</v>
+      </c>
+      <c r="U26">
+        <v>0.0457</v>
+      </c>
+      <c r="V26">
+        <v>0.16</v>
+      </c>
+      <c r="W26">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>17.85554159462938</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.159251124520582</v>
+      </c>
+      <c r="C27">
+        <v>16.43727186077432</v>
+      </c>
+      <c r="D27">
+        <v>20.50327186077432</v>
+      </c>
+      <c r="E27">
+        <v>5.292000000000001</v>
+      </c>
+      <c r="F27">
+        <v>5.336</v>
+      </c>
+      <c r="G27">
+        <v>1.27</v>
+      </c>
+      <c r="H27">
+        <v>21.3</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>6.06</v>
+      </c>
+      <c r="K27">
+        <v>1.88</v>
+      </c>
+      <c r="L27">
+        <v>4.18</v>
+      </c>
+      <c r="M27">
+        <v>0.2438552</v>
+      </c>
+      <c r="N27">
+        <v>3.9361448</v>
+      </c>
+      <c r="O27">
+        <v>0.6297831680000001</v>
+      </c>
+      <c r="P27">
+        <v>3.306361632</v>
+      </c>
+      <c r="Q27">
+        <v>5.186361632</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1995388326941094</v>
+      </c>
+      <c r="T27">
+        <v>1.655789009990339</v>
+      </c>
+      <c r="U27">
+        <v>0.0457</v>
+      </c>
+      <c r="V27">
+        <v>0.16</v>
+      </c>
+      <c r="W27">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>17.1413199308442</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1590460809797144</v>
+      </c>
+      <c r="C28">
+        <v>16.2413607477867</v>
+      </c>
+      <c r="D28">
+        <v>20.5208007477867</v>
+      </c>
+      <c r="E28">
+        <v>5.505440000000001</v>
+      </c>
+      <c r="F28">
+        <v>5.549440000000001</v>
+      </c>
+      <c r="G28">
+        <v>1.27</v>
+      </c>
+      <c r="H28">
+        <v>21.3</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>6.06</v>
+      </c>
+      <c r="K28">
+        <v>1.88</v>
+      </c>
+      <c r="L28">
+        <v>4.18</v>
+      </c>
+      <c r="M28">
+        <v>0.253609408</v>
+      </c>
+      <c r="N28">
+        <v>3.926390592</v>
+      </c>
+      <c r="O28">
+        <v>0.62822249472</v>
+      </c>
+      <c r="P28">
+        <v>3.29816809728</v>
+      </c>
+      <c r="Q28">
+        <v>5.178168097279999</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.2014394607833978</v>
+      </c>
+      <c r="T28">
+        <v>1.675367596257116</v>
+      </c>
+      <c r="U28">
+        <v>0.0457</v>
+      </c>
+      <c r="V28">
+        <v>0.16</v>
+      </c>
+      <c r="W28">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>16.4820383950425</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1588410374388468</v>
+      </c>
+      <c r="C29">
+        <v>16.04547963243013</v>
+      </c>
+      <c r="D29">
+        <v>20.53835963243013</v>
+      </c>
+      <c r="E29">
+        <v>5.718880000000001</v>
+      </c>
+      <c r="F29">
+        <v>5.762880000000001</v>
+      </c>
+      <c r="G29">
+        <v>1.27</v>
+      </c>
+      <c r="H29">
+        <v>21.3</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>6.06</v>
+      </c>
+      <c r="K29">
+        <v>1.88</v>
+      </c>
+      <c r="L29">
+        <v>4.18</v>
+      </c>
+      <c r="M29">
+        <v>0.2633636160000001</v>
+      </c>
+      <c r="N29">
+        <v>3.916636384</v>
+      </c>
+      <c r="O29">
+        <v>0.62666182144</v>
+      </c>
+      <c r="P29">
+        <v>3.28997456256</v>
+      </c>
+      <c r="Q29">
+        <v>5.16997456256</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.2033921608751325</v>
+      </c>
+      <c r="T29">
+        <v>1.695482582147641</v>
+      </c>
+      <c r="U29">
+        <v>0.0457</v>
+      </c>
+      <c r="V29">
+        <v>0.16</v>
+      </c>
+      <c r="W29">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>15.87159252855944</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1586359938979791</v>
+      </c>
+      <c r="C30">
+        <v>15.84962859177415</v>
+      </c>
+      <c r="D30">
+        <v>20.55594859177415</v>
+      </c>
+      <c r="E30">
+        <v>5.932320000000002</v>
+      </c>
+      <c r="F30">
+        <v>5.976320000000001</v>
+      </c>
+      <c r="G30">
+        <v>1.27</v>
+      </c>
+      <c r="H30">
+        <v>21.3</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>6.06</v>
+      </c>
+      <c r="K30">
+        <v>1.88</v>
+      </c>
+      <c r="L30">
+        <v>4.18</v>
+      </c>
+      <c r="M30">
+        <v>0.2731178240000001</v>
+      </c>
+      <c r="N30">
+        <v>3.906882176</v>
+      </c>
+      <c r="O30">
+        <v>0.6251011481600001</v>
+      </c>
+      <c r="P30">
+        <v>3.28178102784</v>
+      </c>
+      <c r="Q30">
+        <v>5.16178102784</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.2053991026360821</v>
+      </c>
+      <c r="T30">
+        <v>1.716156317646236</v>
+      </c>
+      <c r="U30">
+        <v>0.0457</v>
+      </c>
+      <c r="V30">
+        <v>0.16</v>
+      </c>
+      <c r="W30">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>15.30474993825375</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1584309503571115</v>
+      </c>
+      <c r="C31">
+        <v>15.65380770315248</v>
+      </c>
+      <c r="D31">
+        <v>20.57356770315248</v>
+      </c>
+      <c r="E31">
+        <v>6.14576</v>
+      </c>
+      <c r="F31">
+        <v>6.18976</v>
+      </c>
+      <c r="G31">
+        <v>1.27</v>
+      </c>
+      <c r="H31">
+        <v>21.3</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>6.06</v>
+      </c>
+      <c r="K31">
+        <v>1.88</v>
+      </c>
+      <c r="L31">
+        <v>4.18</v>
+      </c>
+      <c r="M31">
+        <v>0.282872032</v>
+      </c>
+      <c r="N31">
+        <v>3.897127967999999</v>
+      </c>
+      <c r="O31">
+        <v>0.6235404748800001</v>
+      </c>
+      <c r="P31">
+        <v>3.27358749312</v>
+      </c>
+      <c r="Q31">
+        <v>5.15358749312</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.2074625779677626</v>
+      </c>
+      <c r="T31">
+        <v>1.737412411891271</v>
+      </c>
+      <c r="U31">
+        <v>0.0457</v>
+      </c>
+      <c r="V31">
+        <v>0.16</v>
+      </c>
+      <c r="W31">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>14.77699994038293</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1582259068162438</v>
+      </c>
+      <c r="C32">
+        <v>15.45801704416425</v>
+      </c>
+      <c r="D32">
+        <v>20.59121704416425</v>
+      </c>
+      <c r="E32">
+        <v>6.3592</v>
+      </c>
+      <c r="F32">
+        <v>6.4032</v>
+      </c>
+      <c r="G32">
+        <v>1.27</v>
+      </c>
+      <c r="H32">
+        <v>21.3</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>6.06</v>
+      </c>
+      <c r="K32">
+        <v>1.88</v>
+      </c>
+      <c r="L32">
+        <v>4.18</v>
+      </c>
+      <c r="M32">
+        <v>0.29262624</v>
+      </c>
+      <c r="N32">
+        <v>3.88737376</v>
+      </c>
+      <c r="O32">
+        <v>0.6219798016000001</v>
+      </c>
+      <c r="P32">
+        <v>3.265393958399999</v>
+      </c>
+      <c r="Q32">
+        <v>5.1453939584</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.2095850097374912</v>
+      </c>
+      <c r="T32">
+        <v>1.759275823114735</v>
+      </c>
+      <c r="U32">
+        <v>0.0457</v>
+      </c>
+      <c r="V32">
+        <v>0.16</v>
+      </c>
+      <c r="W32">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>14.2844332757035</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1580208632753762</v>
+      </c>
+      <c r="C33">
+        <v>15.26225669267507</v>
+      </c>
+      <c r="D33">
+        <v>20.60889669267507</v>
+      </c>
+      <c r="E33">
+        <v>6.572640000000001</v>
+      </c>
+      <c r="F33">
+        <v>6.61664</v>
+      </c>
+      <c r="G33">
+        <v>1.27</v>
+      </c>
+      <c r="H33">
+        <v>21.3</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>6.06</v>
+      </c>
+      <c r="K33">
+        <v>1.88</v>
+      </c>
+      <c r="L33">
+        <v>4.18</v>
+      </c>
+      <c r="M33">
+        <v>0.302380448</v>
+      </c>
+      <c r="N33">
+        <v>3.877619552</v>
+      </c>
+      <c r="O33">
+        <v>0.62041912832</v>
+      </c>
+      <c r="P33">
+        <v>3.25720042368</v>
+      </c>
+      <c r="Q33">
+        <v>5.13720042368</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.2117689612686612</v>
+      </c>
+      <c r="T33">
+        <v>1.781772956402647</v>
+      </c>
+      <c r="U33">
+        <v>0.0457</v>
+      </c>
+      <c r="V33">
+        <v>0.16</v>
+      </c>
+      <c r="W33">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>13.82364510551952</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1578158197345085</v>
+      </c>
+      <c r="C34">
+        <v>15.06652672681821</v>
+      </c>
+      <c r="D34">
+        <v>20.62660672681821</v>
+      </c>
+      <c r="E34">
+        <v>6.786080000000001</v>
+      </c>
+      <c r="F34">
+        <v>6.830080000000001</v>
+      </c>
+      <c r="G34">
+        <v>1.27</v>
+      </c>
+      <c r="H34">
+        <v>21.3</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>6.06</v>
+      </c>
+      <c r="K34">
+        <v>1.88</v>
+      </c>
+      <c r="L34">
+        <v>4.18</v>
+      </c>
+      <c r="M34">
+        <v>0.3121346560000001</v>
+      </c>
+      <c r="N34">
+        <v>3.867865344</v>
+      </c>
+      <c r="O34">
+        <v>0.61885845504</v>
+      </c>
+      <c r="P34">
+        <v>3.249006888959999</v>
+      </c>
+      <c r="Q34">
+        <v>5.129006888959999</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.2140171466683949</v>
+      </c>
+      <c r="T34">
+        <v>1.80493177008138</v>
+      </c>
+      <c r="U34">
+        <v>0.0457</v>
+      </c>
+      <c r="V34">
+        <v>0.16</v>
+      </c>
+      <c r="W34">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>13.39165619597203</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1576107761936409</v>
+      </c>
+      <c r="C35">
+        <v>14.87082722499576</v>
+      </c>
+      <c r="D35">
+        <v>20.64434722499576</v>
+      </c>
+      <c r="E35">
+        <v>6.999520000000001</v>
+      </c>
+      <c r="F35">
+        <v>7.043520000000001</v>
+      </c>
+      <c r="G35">
+        <v>1.27</v>
+      </c>
+      <c r="H35">
+        <v>21.3</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>6.06</v>
+      </c>
+      <c r="K35">
+        <v>1.88</v>
+      </c>
+      <c r="L35">
+        <v>4.18</v>
+      </c>
+      <c r="M35">
+        <v>0.3218888640000001</v>
+      </c>
+      <c r="N35">
+        <v>3.858111136</v>
+      </c>
+      <c r="O35">
+        <v>0.6172977817600001</v>
+      </c>
+      <c r="P35">
+        <v>3.24081335424</v>
+      </c>
+      <c r="Q35">
+        <v>5.120813354239999</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2163324420800611</v>
+      </c>
+      <c r="T35">
+        <v>1.82878189163112</v>
+      </c>
+      <c r="U35">
+        <v>0.0457</v>
+      </c>
+      <c r="V35">
+        <v>0.16</v>
+      </c>
+      <c r="W35">
+        <v>0.03838800000000001</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>12.98584843245773</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1578626926527733</v>
+      </c>
+      <c r="C36">
+        <v>14.63559553284321</v>
+      </c>
+      <c r="D36">
+        <v>20.62255553284321</v>
+      </c>
+      <c r="E36">
+        <v>7.212960000000002</v>
+      </c>
+      <c r="F36">
+        <v>7.256960000000001</v>
+      </c>
+      <c r="G36">
+        <v>1.27</v>
+      </c>
+      <c r="H36">
+        <v>21.3</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>6.06</v>
+      </c>
+      <c r="K36">
+        <v>1.88</v>
+      </c>
+      <c r="L36">
+        <v>4.18</v>
+      </c>
+      <c r="M36">
+        <v>0.3432542080000001</v>
+      </c>
+      <c r="N36">
+        <v>3.836745791999999</v>
+      </c>
+      <c r="O36">
+        <v>0.61387932672</v>
+      </c>
+      <c r="P36">
+        <v>3.222866465279999</v>
+      </c>
+      <c r="Q36">
+        <v>5.102866465279999</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.2187178979587474</v>
+      </c>
+      <c r="T36">
+        <v>1.853354744136913</v>
+      </c>
+      <c r="U36">
+        <v>0.0473</v>
+      </c>
+      <c r="V36">
+        <v>0.16</v>
+      </c>
+      <c r="W36">
+        <v>0.039732</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>12.1775637489053</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1576710891119056</v>
+      </c>
+      <c r="C37">
+        <v>14.43872574558921</v>
+      </c>
+      <c r="D37">
+        <v>20.63912574558921</v>
+      </c>
+      <c r="E37">
+        <v>7.426400000000002</v>
+      </c>
+      <c r="F37">
+        <v>7.470400000000001</v>
+      </c>
+      <c r="G37">
+        <v>1.27</v>
+      </c>
+      <c r="H37">
+        <v>21.3</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>6.06</v>
+      </c>
+      <c r="K37">
+        <v>1.88</v>
+      </c>
+      <c r="L37">
+        <v>4.18</v>
+      </c>
+      <c r="M37">
+        <v>0.3533499200000001</v>
+      </c>
+      <c r="N37">
+        <v>3.826650079999999</v>
+      </c>
+      <c r="O37">
+        <v>0.6122640128</v>
+      </c>
+      <c r="P37">
+        <v>3.2143860672</v>
+      </c>
+      <c r="Q37">
+        <v>5.094386067199999</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.2211767524798549</v>
+      </c>
+      <c r="T37">
+        <v>1.878683684412115</v>
+      </c>
+      <c r="U37">
+        <v>0.0473</v>
+      </c>
+      <c r="V37">
+        <v>0.16</v>
+      </c>
+      <c r="W37">
+        <v>0.039732</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>11.82963335607943</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.157479485571038</v>
+      </c>
+      <c r="C38">
+        <v>14.24188260806306</v>
+      </c>
+      <c r="D38">
+        <v>20.65572260806306</v>
+      </c>
+      <c r="E38">
+        <v>7.63984</v>
+      </c>
+      <c r="F38">
+        <v>7.68384</v>
+      </c>
+      <c r="G38">
+        <v>1.27</v>
+      </c>
+      <c r="H38">
+        <v>21.3</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>6.06</v>
+      </c>
+      <c r="K38">
+        <v>1.88</v>
+      </c>
+      <c r="L38">
+        <v>4.18</v>
+      </c>
+      <c r="M38">
+        <v>0.363445632</v>
+      </c>
+      <c r="N38">
+        <v>3.816554368</v>
+      </c>
+      <c r="O38">
+        <v>0.6106486988800001</v>
+      </c>
+      <c r="P38">
+        <v>3.20590566912</v>
+      </c>
+      <c r="Q38">
+        <v>5.08590566912</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.2237124462047469</v>
+      </c>
+      <c r="T38">
+        <v>1.904804154070917</v>
+      </c>
+      <c r="U38">
+        <v>0.0473</v>
+      </c>
+      <c r="V38">
+        <v>0.16</v>
+      </c>
+      <c r="W38">
+        <v>0.039732</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>11.50103242952167</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1572878820301704</v>
+      </c>
+      <c r="C39">
+        <v>14.0450661846073</v>
+      </c>
+      <c r="D39">
+        <v>20.6723461846073</v>
+      </c>
+      <c r="E39">
+        <v>7.853280000000001</v>
+      </c>
+      <c r="F39">
+        <v>7.89728</v>
+      </c>
+      <c r="G39">
+        <v>1.27</v>
+      </c>
+      <c r="H39">
+        <v>21.3</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>6.06</v>
+      </c>
+      <c r="K39">
+        <v>1.88</v>
+      </c>
+      <c r="L39">
+        <v>4.18</v>
+      </c>
+      <c r="M39">
+        <v>0.3735413440000001</v>
+      </c>
+      <c r="N39">
+        <v>3.806458656</v>
+      </c>
+      <c r="O39">
+        <v>0.60903338496</v>
+      </c>
+      <c r="P39">
+        <v>3.19742527104</v>
+      </c>
+      <c r="Q39">
+        <v>5.077425271039999</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.2263286381431276</v>
+      </c>
+      <c r="T39">
+        <v>1.931753844988729</v>
+      </c>
+      <c r="U39">
+        <v>0.0473</v>
+      </c>
+      <c r="V39">
+        <v>0.16</v>
+      </c>
+      <c r="W39">
+        <v>0.039732</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>11.19019371521027</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1570962784893027</v>
+      </c>
+      <c r="C40">
+        <v>13.84827653977172</v>
+      </c>
+      <c r="D40">
+        <v>20.68899653977173</v>
+      </c>
+      <c r="E40">
+        <v>8.06672</v>
+      </c>
+      <c r="F40">
+        <v>8.110720000000001</v>
+      </c>
+      <c r="G40">
+        <v>1.27</v>
+      </c>
+      <c r="H40">
+        <v>21.3</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>6.06</v>
+      </c>
+      <c r="K40">
+        <v>1.88</v>
+      </c>
+      <c r="L40">
+        <v>4.18</v>
+      </c>
+      <c r="M40">
+        <v>0.383637056</v>
+      </c>
+      <c r="N40">
+        <v>3.796362944</v>
+      </c>
+      <c r="O40">
+        <v>0.6074180710400001</v>
+      </c>
+      <c r="P40">
+        <v>3.18894487296</v>
+      </c>
+      <c r="Q40">
+        <v>5.06894487296</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.2290292233698431</v>
+      </c>
+      <c r="T40">
+        <v>1.959572880774856</v>
+      </c>
+      <c r="U40">
+        <v>0.0473</v>
+      </c>
+      <c r="V40">
+        <v>0.16</v>
+      </c>
+      <c r="W40">
+        <v>0.039732</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>10.89571493323106</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1569046749484351</v>
+      </c>
+      <c r="C41">
+        <v>13.65151373831431</v>
+      </c>
+      <c r="D41">
+        <v>20.70567373831431</v>
+      </c>
+      <c r="E41">
+        <v>8.28016</v>
+      </c>
+      <c r="F41">
+        <v>8.324160000000001</v>
+      </c>
+      <c r="G41">
+        <v>1.27</v>
+      </c>
+      <c r="H41">
+        <v>21.3</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>6.06</v>
+      </c>
+      <c r="K41">
+        <v>1.88</v>
+      </c>
+      <c r="L41">
+        <v>4.18</v>
+      </c>
+      <c r="M41">
+        <v>0.3937327680000001</v>
+      </c>
+      <c r="N41">
+        <v>3.786267232</v>
+      </c>
+      <c r="O41">
+        <v>0.6058027571200001</v>
+      </c>
+      <c r="P41">
+        <v>3.18046447488</v>
+      </c>
+      <c r="Q41">
+        <v>5.06046447488</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2318183523744838</v>
+      </c>
+      <c r="T41">
+        <v>1.988304016094956</v>
+      </c>
+      <c r="U41">
+        <v>0.0473</v>
+      </c>
+      <c r="V41">
+        <v>0.16</v>
+      </c>
+      <c r="W41">
+        <v>0.039732</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>10.61633762725077</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1567130714075675</v>
+      </c>
+      <c r="C42">
+        <v>13.45477784520197</v>
+      </c>
+      <c r="D42">
+        <v>20.72237784520198</v>
+      </c>
+      <c r="E42">
+        <v>8.493600000000001</v>
+      </c>
+      <c r="F42">
+        <v>8.537600000000001</v>
+      </c>
+      <c r="G42">
+        <v>1.27</v>
+      </c>
+      <c r="H42">
+        <v>21.3</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>6.06</v>
+      </c>
+      <c r="K42">
+        <v>1.88</v>
+      </c>
+      <c r="L42">
+        <v>4.18</v>
+      </c>
+      <c r="M42">
+        <v>0.40382848</v>
+      </c>
+      <c r="N42">
+        <v>3.77617152</v>
+      </c>
+      <c r="O42">
+        <v>0.6041874432000001</v>
+      </c>
+      <c r="P42">
+        <v>3.171984076799999</v>
+      </c>
+      <c r="Q42">
+        <v>5.051984076799999</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.2347004523459458</v>
+      </c>
+      <c r="T42">
+        <v>2.017992855925725</v>
+      </c>
+      <c r="U42">
+        <v>0.0473</v>
+      </c>
+      <c r="V42">
+        <v>0.16</v>
+      </c>
+      <c r="W42">
+        <v>0.039732</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>10.3509291865695</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1578301878666998</v>
+      </c>
+      <c r="C43">
+        <v>13.14432472990815</v>
+      </c>
+      <c r="D43">
+        <v>20.62536472990815</v>
+      </c>
+      <c r="E43">
+        <v>8.707040000000001</v>
+      </c>
+      <c r="F43">
+        <v>8.751040000000001</v>
+      </c>
+      <c r="G43">
+        <v>1.27</v>
+      </c>
+      <c r="H43">
+        <v>21.3</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>6.06</v>
+      </c>
+      <c r="K43">
+        <v>1.88</v>
+      </c>
+      <c r="L43">
+        <v>4.18</v>
+      </c>
+      <c r="M43">
+        <v>0.4471781440000001</v>
+      </c>
+      <c r="N43">
+        <v>3.732821856</v>
+      </c>
+      <c r="O43">
+        <v>0.59725149696</v>
+      </c>
+      <c r="P43">
+        <v>3.13557035904</v>
+      </c>
+      <c r="Q43">
+        <v>5.01557035904</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2376802506215251</v>
+      </c>
+      <c r="T43">
+        <v>2.04868809710669</v>
+      </c>
+      <c r="U43">
+        <v>0.0511</v>
+      </c>
+      <c r="V43">
+        <v>0.16</v>
+      </c>
+      <c r="W43">
+        <v>0.042924</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>9.347505141038376</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1576705043258322</v>
+      </c>
+      <c r="C44">
+        <v>12.94469635968183</v>
+      </c>
+      <c r="D44">
+        <v>20.63917635968183</v>
+      </c>
+      <c r="E44">
+        <v>8.92048</v>
+      </c>
+      <c r="F44">
+        <v>8.96448</v>
+      </c>
+      <c r="G44">
+        <v>1.27</v>
+      </c>
+      <c r="H44">
+        <v>21.3</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>6.06</v>
+      </c>
+      <c r="K44">
+        <v>1.88</v>
+      </c>
+      <c r="L44">
+        <v>4.18</v>
+      </c>
+      <c r="M44">
+        <v>0.458084928</v>
+      </c>
+      <c r="N44">
+        <v>3.721915072</v>
+      </c>
+      <c r="O44">
+        <v>0.5955064115200001</v>
+      </c>
+      <c r="P44">
+        <v>3.12640866048</v>
+      </c>
+      <c r="Q44">
+        <v>5.00640866048</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2407628005617796</v>
+      </c>
+      <c r="T44">
+        <v>2.080441794880102</v>
+      </c>
+      <c r="U44">
+        <v>0.0511</v>
+      </c>
+      <c r="V44">
+        <v>0.16</v>
+      </c>
+      <c r="W44">
+        <v>0.042924</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>9.124945494823178</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1575108207849646</v>
+      </c>
+      <c r="C45">
+        <v>12.74508649957128</v>
+      </c>
+      <c r="D45">
+        <v>20.65300649957128</v>
+      </c>
+      <c r="E45">
+        <v>9.13392</v>
+      </c>
+      <c r="F45">
+        <v>9.17792</v>
+      </c>
+      <c r="G45">
+        <v>1.27</v>
+      </c>
+      <c r="H45">
+        <v>21.3</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>6.06</v>
+      </c>
+      <c r="K45">
+        <v>1.88</v>
+      </c>
+      <c r="L45">
+        <v>4.18</v>
+      </c>
+      <c r="M45">
+        <v>0.468991712</v>
+      </c>
+      <c r="N45">
+        <v>3.711008287999999</v>
+      </c>
+      <c r="O45">
+        <v>0.59376132608</v>
+      </c>
+      <c r="P45">
+        <v>3.117246961919999</v>
+      </c>
+      <c r="Q45">
+        <v>4.997246961919999</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2439535101490606</v>
+      </c>
+      <c r="T45">
+        <v>2.113309657487669</v>
+      </c>
+      <c r="U45">
+        <v>0.0511</v>
+      </c>
+      <c r="V45">
+        <v>0.16</v>
+      </c>
+      <c r="W45">
+        <v>0.042924</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>8.912737460059848</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1573511372440969</v>
+      </c>
+      <c r="C46">
+        <v>12.54549518681187</v>
+      </c>
+      <c r="D46">
+        <v>20.66685518681187</v>
+      </c>
+      <c r="E46">
+        <v>9.34736</v>
+      </c>
+      <c r="F46">
+        <v>9.391360000000001</v>
+      </c>
+      <c r="G46">
+        <v>1.27</v>
+      </c>
+      <c r="H46">
+        <v>21.3</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>6.06</v>
+      </c>
+      <c r="K46">
+        <v>1.88</v>
+      </c>
+      <c r="L46">
+        <v>4.18</v>
+      </c>
+      <c r="M46">
+        <v>0.479898496</v>
+      </c>
+      <c r="N46">
+        <v>3.700101504</v>
+      </c>
+      <c r="O46">
+        <v>0.59201624064</v>
+      </c>
+      <c r="P46">
+        <v>3.10808526336</v>
+      </c>
+      <c r="Q46">
+        <v>4.988085263359999</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2472581736501731</v>
+      </c>
+      <c r="T46">
+        <v>2.14735137233122</v>
+      </c>
+      <c r="U46">
+        <v>0.0511</v>
+      </c>
+      <c r="V46">
+        <v>0.16</v>
+      </c>
+      <c r="W46">
+        <v>0.042924</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>8.710175245058487</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1571914537032293</v>
+      </c>
+      <c r="C47">
+        <v>12.34592245873891</v>
+      </c>
+      <c r="D47">
+        <v>20.68072245873891</v>
+      </c>
+      <c r="E47">
+        <v>9.5608</v>
+      </c>
+      <c r="F47">
+        <v>9.604800000000001</v>
+      </c>
+      <c r="G47">
+        <v>1.27</v>
+      </c>
+      <c r="H47">
+        <v>21.3</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>6.06</v>
+      </c>
+      <c r="K47">
+        <v>1.88</v>
+      </c>
+      <c r="L47">
+        <v>4.18</v>
+      </c>
+      <c r="M47">
+        <v>0.4908052800000001</v>
+      </c>
+      <c r="N47">
+        <v>3.68919472</v>
+      </c>
+      <c r="O47">
+        <v>0.5902711552000001</v>
+      </c>
+      <c r="P47">
+        <v>3.0989235648</v>
+      </c>
+      <c r="Q47">
+        <v>4.9789235648</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2506830067331441</v>
+      </c>
+      <c r="T47">
+        <v>2.182630967714537</v>
+      </c>
+      <c r="U47">
+        <v>0.0511</v>
+      </c>
+      <c r="V47">
+        <v>0.16</v>
+      </c>
+      <c r="W47">
+        <v>0.042924</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>8.516615795168299</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1570317701623617</v>
+      </c>
+      <c r="C48">
+        <v>12.14636835278799</v>
+      </c>
+      <c r="D48">
+        <v>20.69460835278799</v>
+      </c>
+      <c r="E48">
+        <v>9.774240000000001</v>
+      </c>
+      <c r="F48">
+        <v>9.818240000000001</v>
+      </c>
+      <c r="G48">
+        <v>1.27</v>
+      </c>
+      <c r="H48">
+        <v>21.3</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>6.06</v>
+      </c>
+      <c r="K48">
+        <v>1.88</v>
+      </c>
+      <c r="L48">
+        <v>4.18</v>
+      </c>
+      <c r="M48">
+        <v>0.501712064</v>
+      </c>
+      <c r="N48">
+        <v>3.678287936</v>
+      </c>
+      <c r="O48">
+        <v>0.5885260697600001</v>
+      </c>
+      <c r="P48">
+        <v>3.08976186624</v>
+      </c>
+      <c r="Q48">
+        <v>4.96976186624</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2542346854858549</v>
+      </c>
+      <c r="T48">
+        <v>2.219217214778717</v>
+      </c>
+      <c r="U48">
+        <v>0.0511</v>
+      </c>
+      <c r="V48">
+        <v>0.16</v>
+      </c>
+      <c r="W48">
+        <v>0.042924</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>8.331471973534207</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.156872086621494</v>
+      </c>
+      <c r="C49">
+        <v>11.94683290649531</v>
+      </c>
+      <c r="D49">
+        <v>20.70851290649531</v>
+      </c>
+      <c r="E49">
+        <v>9.987680000000001</v>
+      </c>
+      <c r="F49">
+        <v>10.03168</v>
+      </c>
+      <c r="G49">
+        <v>1.27</v>
+      </c>
+      <c r="H49">
+        <v>21.3</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>6.06</v>
+      </c>
+      <c r="K49">
+        <v>1.88</v>
+      </c>
+      <c r="L49">
+        <v>4.18</v>
+      </c>
+      <c r="M49">
+        <v>0.5126188480000001</v>
+      </c>
+      <c r="N49">
+        <v>3.667381151999999</v>
+      </c>
+      <c r="O49">
+        <v>0.58678098432</v>
+      </c>
+      <c r="P49">
+        <v>3.080600167679999</v>
+      </c>
+      <c r="Q49">
+        <v>4.960600167679999</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2579203898518755</v>
+      </c>
+      <c r="T49">
+        <v>2.25718407493966</v>
+      </c>
+      <c r="U49">
+        <v>0.0511</v>
+      </c>
+      <c r="V49">
+        <v>0.16</v>
+      </c>
+      <c r="W49">
+        <v>0.042924</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>8.154206612395178</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1567124030806264</v>
+      </c>
+      <c r="C50">
+        <v>11.747316157498</v>
+      </c>
+      <c r="D50">
+        <v>20.722436157498</v>
+      </c>
+      <c r="E50">
+        <v>10.20112</v>
+      </c>
+      <c r="F50">
+        <v>10.24512</v>
+      </c>
+      <c r="G50">
+        <v>1.27</v>
+      </c>
+      <c r="H50">
+        <v>21.3</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>6.06</v>
+      </c>
+      <c r="K50">
+        <v>1.88</v>
+      </c>
+      <c r="L50">
+        <v>4.18</v>
+      </c>
+      <c r="M50">
+        <v>0.523525632</v>
+      </c>
+      <c r="N50">
+        <v>3.656474368</v>
+      </c>
+      <c r="O50">
+        <v>0.5850358988800001</v>
+      </c>
+      <c r="P50">
+        <v>3.071438469119999</v>
+      </c>
+      <c r="Q50">
+        <v>4.951438469119999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2617478520781277</v>
+      </c>
+      <c r="T50">
+        <v>2.296611198952946</v>
+      </c>
+      <c r="U50">
+        <v>0.0511</v>
+      </c>
+      <c r="V50">
+        <v>0.16</v>
+      </c>
+      <c r="W50">
+        <v>0.042924</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>7.98432730797028</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1565527195397587</v>
+      </c>
+      <c r="C51">
+        <v>11.5478181435345</v>
+      </c>
+      <c r="D51">
+        <v>20.73637814353451</v>
+      </c>
+      <c r="E51">
+        <v>10.41456</v>
+      </c>
+      <c r="F51">
+        <v>10.45856</v>
+      </c>
+      <c r="G51">
+        <v>1.27</v>
+      </c>
+      <c r="H51">
+        <v>21.3</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>6.06</v>
+      </c>
+      <c r="K51">
+        <v>1.88</v>
+      </c>
+      <c r="L51">
+        <v>4.18</v>
+      </c>
+      <c r="M51">
+        <v>0.534432416</v>
+      </c>
+      <c r="N51">
+        <v>3.645567584</v>
+      </c>
+      <c r="O51">
+        <v>0.5832908134400001</v>
+      </c>
+      <c r="P51">
+        <v>3.06227677056</v>
+      </c>
+      <c r="Q51">
+        <v>4.942276770559999</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2657254108622721</v>
+      </c>
+      <c r="T51">
+        <v>2.337584484692243</v>
+      </c>
+      <c r="U51">
+        <v>0.0511</v>
+      </c>
+      <c r="V51">
+        <v>0.16</v>
+      </c>
+      <c r="W51">
+        <v>0.042924</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>7.821381852705581</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1571910359988911</v>
+      </c>
+      <c r="C52">
+        <v>11.27875875751113</v>
+      </c>
+      <c r="D52">
+        <v>20.68075875751114</v>
+      </c>
+      <c r="E52">
+        <v>10.628</v>
+      </c>
+      <c r="F52">
+        <v>10.672</v>
+      </c>
+      <c r="G52">
+        <v>1.27</v>
+      </c>
+      <c r="H52">
+        <v>21.3</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>6.06</v>
+      </c>
+      <c r="K52">
+        <v>1.88</v>
+      </c>
+      <c r="L52">
+        <v>4.18</v>
+      </c>
+      <c r="M52">
+        <v>0.5656160000000001</v>
+      </c>
+      <c r="N52">
+        <v>3.614383999999999</v>
+      </c>
+      <c r="O52">
+        <v>0.5783014400000001</v>
+      </c>
+      <c r="P52">
+        <v>3.036082559999999</v>
+      </c>
+      <c r="Q52">
+        <v>4.91608256</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2698620719977822</v>
+      </c>
+      <c r="T52">
+        <v>2.380196701861112</v>
+      </c>
+      <c r="U52">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V52">
+        <v>0.16</v>
+      </c>
+      <c r="W52">
+        <v>0.04452</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>7.390172838109245</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1570473124580235</v>
+      </c>
+      <c r="C53">
+        <v>11.07781599382603</v>
+      </c>
+      <c r="D53">
+        <v>20.69325599382603</v>
+      </c>
+      <c r="E53">
+        <v>10.84144</v>
+      </c>
+      <c r="F53">
+        <v>10.88544</v>
+      </c>
+      <c r="G53">
+        <v>1.27</v>
+      </c>
+      <c r="H53">
+        <v>21.3</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>6.06</v>
+      </c>
+      <c r="K53">
+        <v>1.88</v>
+      </c>
+      <c r="L53">
+        <v>4.18</v>
+      </c>
+      <c r="M53">
+        <v>0.5769283200000002</v>
+      </c>
+      <c r="N53">
+        <v>3.603071679999999</v>
+      </c>
+      <c r="O53">
+        <v>0.5764914688</v>
+      </c>
+      <c r="P53">
+        <v>3.026580211199999</v>
+      </c>
+      <c r="Q53">
+        <v>4.9065802112</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2741675764449458</v>
+      </c>
+      <c r="T53">
+        <v>2.424548193200139</v>
+      </c>
+      <c r="U53">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V53">
+        <v>0.16</v>
+      </c>
+      <c r="W53">
+        <v>0.04452</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>7.245267488342396</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1569035889171558</v>
+      </c>
+      <c r="C54">
+        <v>10.87688834325679</v>
+      </c>
+      <c r="D54">
+        <v>20.70576834325679</v>
+      </c>
+      <c r="E54">
+        <v>11.05488</v>
+      </c>
+      <c r="F54">
+        <v>11.09888</v>
+      </c>
+      <c r="G54">
+        <v>1.27</v>
+      </c>
+      <c r="H54">
+        <v>21.3</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>6.06</v>
+      </c>
+      <c r="K54">
+        <v>1.88</v>
+      </c>
+      <c r="L54">
+        <v>4.18</v>
+      </c>
+      <c r="M54">
+        <v>0.5882406400000001</v>
+      </c>
+      <c r="N54">
+        <v>3.59175936</v>
+      </c>
+      <c r="O54">
+        <v>0.5746814976000001</v>
+      </c>
+      <c r="P54">
+        <v>3.0170778624</v>
+      </c>
+      <c r="Q54">
+        <v>4.8970778624</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2786524769107414</v>
+      </c>
+      <c r="T54">
+        <v>2.470747663344959</v>
+      </c>
+      <c r="U54">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V54">
+        <v>0.16</v>
+      </c>
+      <c r="W54">
+        <v>0.04452</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>7.105935421258891</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1567598653762882</v>
+      </c>
+      <c r="C55">
+        <v>10.67597583323481</v>
+      </c>
+      <c r="D55">
+        <v>20.71829583323481</v>
+      </c>
+      <c r="E55">
+        <v>11.26832</v>
+      </c>
+      <c r="F55">
+        <v>11.31232</v>
+      </c>
+      <c r="G55">
+        <v>1.27</v>
+      </c>
+      <c r="H55">
+        <v>21.3</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>6.06</v>
+      </c>
+      <c r="K55">
+        <v>1.88</v>
+      </c>
+      <c r="L55">
+        <v>4.18</v>
+      </c>
+      <c r="M55">
+        <v>0.5995529600000001</v>
+      </c>
+      <c r="N55">
+        <v>3.58044704</v>
+      </c>
+      <c r="O55">
+        <v>0.5728715264000001</v>
+      </c>
+      <c r="P55">
+        <v>3.0075755136</v>
+      </c>
+      <c r="Q55">
+        <v>4.8875755136</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2833282242048685</v>
+      </c>
+      <c r="T55">
+        <v>2.518913068389558</v>
+      </c>
+      <c r="U55">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V55">
+        <v>0.16</v>
+      </c>
+      <c r="W55">
+        <v>0.04452</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>6.97186116802759</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1566161418354206</v>
+      </c>
+      <c r="C56">
+        <v>10.47507849125792</v>
+      </c>
+      <c r="D56">
+        <v>20.73083849125792</v>
+      </c>
+      <c r="E56">
+        <v>11.48176</v>
+      </c>
+      <c r="F56">
+        <v>11.52576</v>
+      </c>
+      <c r="G56">
+        <v>1.27</v>
+      </c>
+      <c r="H56">
+        <v>21.3</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>6.06</v>
+      </c>
+      <c r="K56">
+        <v>1.88</v>
+      </c>
+      <c r="L56">
+        <v>4.18</v>
+      </c>
+      <c r="M56">
+        <v>0.6108652800000002</v>
+      </c>
+      <c r="N56">
+        <v>3.56913472</v>
+      </c>
+      <c r="O56">
+        <v>0.5710615552</v>
+      </c>
+      <c r="P56">
+        <v>2.9980731648</v>
+      </c>
+      <c r="Q56">
+        <v>4.8780731648</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2882072648596099</v>
+      </c>
+      <c r="T56">
+        <v>2.569172621479574</v>
+      </c>
+      <c r="U56">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V56">
+        <v>0.16</v>
+      </c>
+      <c r="W56">
+        <v>0.04452</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>6.84275262787893</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1564724182945529</v>
+      </c>
+      <c r="C57">
+        <v>10.27419634489058</v>
+      </c>
+      <c r="D57">
+        <v>20.74339634489058</v>
+      </c>
+      <c r="E57">
+        <v>11.6952</v>
+      </c>
+      <c r="F57">
+        <v>11.7392</v>
+      </c>
+      <c r="G57">
+        <v>1.27</v>
+      </c>
+      <c r="H57">
+        <v>21.3</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>6.06</v>
+      </c>
+      <c r="K57">
+        <v>1.88</v>
+      </c>
+      <c r="L57">
+        <v>4.18</v>
+      </c>
+      <c r="M57">
+        <v>0.6221776000000002</v>
+      </c>
+      <c r="N57">
+        <v>3.5578224</v>
+      </c>
+      <c r="O57">
+        <v>0.5692515840000001</v>
+      </c>
+      <c r="P57">
+        <v>2.988570815999999</v>
+      </c>
+      <c r="Q57">
+        <v>4.868570815999999</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2933031517656732</v>
+      </c>
+      <c r="T57">
+        <v>2.621665932484703</v>
+      </c>
+      <c r="U57">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V57">
+        <v>0.16</v>
+      </c>
+      <c r="W57">
+        <v>0.04452</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>6.718338943735676</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1563286947536853</v>
+      </c>
+      <c r="C58">
+        <v>10.07332942176406</v>
+      </c>
+      <c r="D58">
+        <v>20.75596942176406</v>
+      </c>
+      <c r="E58">
+        <v>11.90864</v>
+      </c>
+      <c r="F58">
+        <v>11.95264</v>
+      </c>
+      <c r="G58">
+        <v>1.27</v>
+      </c>
+      <c r="H58">
+        <v>21.3</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>6.06</v>
+      </c>
+      <c r="K58">
+        <v>1.88</v>
+      </c>
+      <c r="L58">
+        <v>4.18</v>
+      </c>
+      <c r="M58">
+        <v>0.6334899200000002</v>
+      </c>
+      <c r="N58">
+        <v>3.54651008</v>
+      </c>
+      <c r="O58">
+        <v>0.5674416128000001</v>
+      </c>
+      <c r="P58">
+        <v>2.979068467199999</v>
+      </c>
+      <c r="Q58">
+        <v>4.859068467199999</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2986306698947393</v>
+      </c>
+      <c r="T58">
+        <v>2.676545303080974</v>
+      </c>
+      <c r="U58">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V58">
+        <v>0.16</v>
+      </c>
+      <c r="W58">
+        <v>0.04452</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>6.598368605454683</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1561849712128176</v>
+      </c>
+      <c r="C59">
+        <v>9.87247774957669</v>
+      </c>
+      <c r="D59">
+        <v>20.76855774957669</v>
+      </c>
+      <c r="E59">
+        <v>12.12208</v>
+      </c>
+      <c r="F59">
+        <v>12.16608</v>
+      </c>
+      <c r="G59">
+        <v>1.27</v>
+      </c>
+      <c r="H59">
+        <v>21.3</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>6.06</v>
+      </c>
+      <c r="K59">
+        <v>1.88</v>
+      </c>
+      <c r="L59">
+        <v>4.18</v>
+      </c>
+      <c r="M59">
+        <v>0.6448022400000002</v>
+      </c>
+      <c r="N59">
+        <v>3.53519776</v>
+      </c>
+      <c r="O59">
+        <v>0.5656316416</v>
+      </c>
+      <c r="P59">
+        <v>2.9695661184</v>
+      </c>
+      <c r="Q59">
+        <v>4.849566118399999</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.3042059795646922</v>
+      </c>
+      <c r="T59">
+        <v>2.733977202542187</v>
+      </c>
+      <c r="U59">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V59">
+        <v>0.16</v>
+      </c>
+      <c r="W59">
+        <v>0.04452</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>6.482607752727407</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.15604124767195</v>
+      </c>
+      <c r="C60">
+        <v>9.671641356094025</v>
+      </c>
+      <c r="D60">
+        <v>20.78116135609402</v>
+      </c>
+      <c r="E60">
+        <v>12.33552</v>
+      </c>
+      <c r="F60">
+        <v>12.37952</v>
+      </c>
+      <c r="G60">
+        <v>1.27</v>
+      </c>
+      <c r="H60">
+        <v>21.3</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>6.06</v>
+      </c>
+      <c r="K60">
+        <v>1.88</v>
+      </c>
+      <c r="L60">
+        <v>4.18</v>
+      </c>
+      <c r="M60">
+        <v>0.65611456</v>
+      </c>
+      <c r="N60">
+        <v>3.52388544</v>
+      </c>
+      <c r="O60">
+        <v>0.5638216704000001</v>
+      </c>
+      <c r="P60">
+        <v>2.9600637696</v>
+      </c>
+      <c r="Q60">
+        <v>4.8400637696</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.3100467801713095</v>
+      </c>
+      <c r="T60">
+        <v>2.794143954358696</v>
+      </c>
+      <c r="U60">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V60">
+        <v>0.16</v>
+      </c>
+      <c r="W60">
+        <v>0.04452</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>6.370838653542454</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1558975241310824</v>
+      </c>
+      <c r="C61">
+        <v>9.470820269149053</v>
+      </c>
+      <c r="D61">
+        <v>20.79378026914905</v>
+      </c>
+      <c r="E61">
+        <v>12.54896</v>
+      </c>
+      <c r="F61">
+        <v>12.59296</v>
+      </c>
+      <c r="G61">
+        <v>1.27</v>
+      </c>
+      <c r="H61">
+        <v>21.3</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>6.06</v>
+      </c>
+      <c r="K61">
+        <v>1.88</v>
+      </c>
+      <c r="L61">
+        <v>4.18</v>
+      </c>
+      <c r="M61">
+        <v>0.6674268800000001</v>
+      </c>
+      <c r="N61">
+        <v>3.51257312</v>
+      </c>
+      <c r="O61">
+        <v>0.5620116992</v>
+      </c>
+      <c r="P61">
+        <v>2.9505614208</v>
+      </c>
+      <c r="Q61">
+        <v>4.8305614208</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.3161724978806887</v>
+      </c>
+      <c r="T61">
+        <v>2.85724566967845</v>
+      </c>
+      <c r="U61">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V61">
+        <v>0.16</v>
+      </c>
+      <c r="W61">
+        <v>0.04452</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>6.262858337380718</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1567618005902147</v>
+      </c>
+      <c r="C62">
+        <v>9.181727051954223</v>
+      </c>
+      <c r="D62">
+        <v>20.71812705195422</v>
+      </c>
+      <c r="E62">
+        <v>12.7624</v>
+      </c>
+      <c r="F62">
+        <v>12.8064</v>
+      </c>
+      <c r="G62">
+        <v>1.27</v>
+      </c>
+      <c r="H62">
+        <v>21.3</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>6.06</v>
+      </c>
+      <c r="K62">
+        <v>1.88</v>
+      </c>
+      <c r="L62">
+        <v>4.18</v>
+      </c>
+      <c r="M62">
+        <v>0.704352</v>
+      </c>
+      <c r="N62">
+        <v>3.475648</v>
+      </c>
+      <c r="O62">
+        <v>0.5561036800000001</v>
+      </c>
+      <c r="P62">
+        <v>2.91954432</v>
+      </c>
+      <c r="Q62">
+        <v>4.799544319999999</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.3226045014755368</v>
+      </c>
+      <c r="T62">
+        <v>2.923502470764191</v>
+      </c>
+      <c r="U62">
+        <v>0.055</v>
+      </c>
+      <c r="V62">
+        <v>0.16</v>
+      </c>
+      <c r="W62">
+        <v>0.0462</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>5.934532733633183</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1566348770493471</v>
+      </c>
+      <c r="C63">
+        <v>8.979362620850496</v>
+      </c>
+      <c r="D63">
+        <v>20.7292026208505</v>
+      </c>
+      <c r="E63">
+        <v>12.97584</v>
+      </c>
+      <c r="F63">
+        <v>13.01984</v>
+      </c>
+      <c r="G63">
+        <v>1.27</v>
+      </c>
+      <c r="H63">
+        <v>21.3</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>6.06</v>
+      </c>
+      <c r="K63">
+        <v>1.88</v>
+      </c>
+      <c r="L63">
+        <v>4.18</v>
+      </c>
+      <c r="M63">
+        <v>0.7160912</v>
+      </c>
+      <c r="N63">
+        <v>3.4639088</v>
+      </c>
+      <c r="O63">
+        <v>0.5542254080000001</v>
+      </c>
+      <c r="P63">
+        <v>2.909683391999999</v>
+      </c>
+      <c r="Q63">
+        <v>4.789683391999999</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.3293663514085823</v>
+      </c>
+      <c r="T63">
+        <v>2.993157056520997</v>
+      </c>
+      <c r="U63">
+        <v>0.055</v>
+      </c>
+      <c r="V63">
+        <v>0.16</v>
+      </c>
+      <c r="W63">
+        <v>0.0462</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>5.837245311770343</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1565079535084795</v>
+      </c>
+      <c r="C64">
+        <v>8.777010037713293</v>
+      </c>
+      <c r="D64">
+        <v>20.74029003771329</v>
+      </c>
+      <c r="E64">
+        <v>13.18928</v>
+      </c>
+      <c r="F64">
+        <v>13.23328</v>
+      </c>
+      <c r="G64">
+        <v>1.27</v>
+      </c>
+      <c r="H64">
+        <v>21.3</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>6.06</v>
+      </c>
+      <c r="K64">
+        <v>1.88</v>
+      </c>
+      <c r="L64">
+        <v>4.18</v>
+      </c>
+      <c r="M64">
+        <v>0.7278304</v>
+      </c>
+      <c r="N64">
+        <v>3.4521696</v>
+      </c>
+      <c r="O64">
+        <v>0.5523471360000001</v>
+      </c>
+      <c r="P64">
+        <v>2.899822464</v>
+      </c>
+      <c r="Q64">
+        <v>4.779822464</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.3364840881802091</v>
+      </c>
+      <c r="T64">
+        <v>3.066477673107107</v>
+      </c>
+      <c r="U64">
+        <v>0.055</v>
+      </c>
+      <c r="V64">
+        <v>0.16</v>
+      </c>
+      <c r="W64">
+        <v>0.0462</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>5.743096193838564</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1563810299676118</v>
+      </c>
+      <c r="C65">
+        <v>8.574669321564132</v>
+      </c>
+      <c r="D65">
+        <v>20.75138932156413</v>
+      </c>
+      <c r="E65">
+        <v>13.40272</v>
+      </c>
+      <c r="F65">
+        <v>13.44672</v>
+      </c>
+      <c r="G65">
+        <v>1.27</v>
+      </c>
+      <c r="H65">
+        <v>21.3</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>6.06</v>
+      </c>
+      <c r="K65">
+        <v>1.88</v>
+      </c>
+      <c r="L65">
+        <v>4.18</v>
+      </c>
+      <c r="M65">
+        <v>0.7395696</v>
+      </c>
+      <c r="N65">
+        <v>3.440430399999999</v>
+      </c>
+      <c r="O65">
+        <v>0.5504688640000001</v>
+      </c>
+      <c r="P65">
+        <v>2.889961535999999</v>
+      </c>
+      <c r="Q65">
+        <v>4.769961535999999</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.343986567480032</v>
+      </c>
+      <c r="T65">
+        <v>3.14376156626544</v>
+      </c>
+      <c r="U65">
+        <v>0.055</v>
+      </c>
+      <c r="V65">
+        <v>0.16</v>
+      </c>
+      <c r="W65">
+        <v>0.0462</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>5.651935936793507</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1562541064267442</v>
+      </c>
+      <c r="C66">
+        <v>8.372340491465273</v>
+      </c>
+      <c r="D66">
+        <v>20.76250049146527</v>
+      </c>
+      <c r="E66">
+        <v>13.61616</v>
+      </c>
+      <c r="F66">
+        <v>13.66016</v>
+      </c>
+      <c r="G66">
+        <v>1.27</v>
+      </c>
+      <c r="H66">
+        <v>21.3</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>6.06</v>
+      </c>
+      <c r="K66">
+        <v>1.88</v>
+      </c>
+      <c r="L66">
+        <v>4.18</v>
+      </c>
+      <c r="M66">
+        <v>0.7513088000000001</v>
+      </c>
+      <c r="N66">
+        <v>3.428691199999999</v>
+      </c>
+      <c r="O66">
+        <v>0.548590592</v>
+      </c>
+      <c r="P66">
+        <v>2.880100607999999</v>
+      </c>
+      <c r="Q66">
+        <v>4.760100607999999</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.3519058511854005</v>
+      </c>
+      <c r="T66">
+        <v>3.22533900904368</v>
+      </c>
+      <c r="U66">
+        <v>0.055</v>
+      </c>
+      <c r="V66">
+        <v>0.16</v>
+      </c>
+      <c r="W66">
+        <v>0.0462</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>5.563624437781108</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1561271828858766</v>
+      </c>
+      <c r="C67">
+        <v>8.170023566519822</v>
+      </c>
+      <c r="D67">
+        <v>20.77362356651982</v>
+      </c>
+      <c r="E67">
+        <v>13.8296</v>
+      </c>
+      <c r="F67">
+        <v>13.8736</v>
+      </c>
+      <c r="G67">
+        <v>1.27</v>
+      </c>
+      <c r="H67">
+        <v>21.3</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>6.06</v>
+      </c>
+      <c r="K67">
+        <v>1.88</v>
+      </c>
+      <c r="L67">
+        <v>4.18</v>
+      </c>
+      <c r="M67">
+        <v>0.7630480000000001</v>
+      </c>
+      <c r="N67">
+        <v>3.416952</v>
+      </c>
+      <c r="O67">
+        <v>0.54671232</v>
+      </c>
+      <c r="P67">
+        <v>2.87023968</v>
+      </c>
+      <c r="Q67">
+        <v>4.75023968</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.3602776653882188</v>
+      </c>
+      <c r="T67">
+        <v>3.311578019980678</v>
+      </c>
+      <c r="U67">
+        <v>0.055</v>
+      </c>
+      <c r="V67">
+        <v>0.16</v>
+      </c>
+      <c r="W67">
+        <v>0.0462</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>5.478030215661399</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1560002593450089</v>
+      </c>
+      <c r="C68">
+        <v>7.967718565871849</v>
+      </c>
+      <c r="D68">
+        <v>20.78475856587185</v>
+      </c>
+      <c r="E68">
+        <v>14.04304</v>
+      </c>
+      <c r="F68">
+        <v>14.08704</v>
+      </c>
+      <c r="G68">
+        <v>1.27</v>
+      </c>
+      <c r="H68">
+        <v>21.3</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>6.06</v>
+      </c>
+      <c r="K68">
+        <v>1.88</v>
+      </c>
+      <c r="L68">
+        <v>4.18</v>
+      </c>
+      <c r="M68">
+        <v>0.7747872000000001</v>
+      </c>
+      <c r="N68">
+        <v>3.4052128</v>
+      </c>
+      <c r="O68">
+        <v>0.544834048</v>
+      </c>
+      <c r="P68">
+        <v>2.860378752</v>
+      </c>
+      <c r="Q68">
+        <v>4.740378752</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.3691419392500263</v>
+      </c>
+      <c r="T68">
+        <v>3.402889913913968</v>
+      </c>
+      <c r="U68">
+        <v>0.055</v>
+      </c>
+      <c r="V68">
+        <v>0.16</v>
+      </c>
+      <c r="W68">
+        <v>0.0462</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>5.395029757848348</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1558733358041413</v>
+      </c>
+      <c r="C69">
+        <v>7.765425508706477</v>
+      </c>
+      <c r="D69">
+        <v>20.79590550870648</v>
+      </c>
+      <c r="E69">
+        <v>14.25648</v>
+      </c>
+      <c r="F69">
+        <v>14.30048</v>
+      </c>
+      <c r="G69">
+        <v>1.27</v>
+      </c>
+      <c r="H69">
+        <v>21.3</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>6.06</v>
+      </c>
+      <c r="K69">
+        <v>1.88</v>
+      </c>
+      <c r="L69">
+        <v>4.18</v>
+      </c>
+      <c r="M69">
+        <v>0.7865264000000001</v>
+      </c>
+      <c r="N69">
+        <v>3.3934736</v>
+      </c>
+      <c r="O69">
+        <v>0.542955776</v>
+      </c>
+      <c r="P69">
+        <v>2.850517824</v>
+      </c>
+      <c r="Q69">
+        <v>4.730517824</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.3785434418307312</v>
+      </c>
+      <c r="T69">
+        <v>3.499735862025035</v>
+      </c>
+      <c r="U69">
+        <v>0.055</v>
+      </c>
+      <c r="V69">
+        <v>0.16</v>
+      </c>
+      <c r="W69">
+        <v>0.0462</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>5.314506925641656</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1557464122632736</v>
+      </c>
+      <c r="C70">
+        <v>7.563144414250036</v>
+      </c>
+      <c r="D70">
+        <v>20.80706441425004</v>
+      </c>
+      <c r="E70">
+        <v>14.46992</v>
+      </c>
+      <c r="F70">
+        <v>14.51392</v>
+      </c>
+      <c r="G70">
+        <v>1.27</v>
+      </c>
+      <c r="H70">
+        <v>21.3</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>6.06</v>
+      </c>
+      <c r="K70">
+        <v>1.88</v>
+      </c>
+      <c r="L70">
+        <v>4.18</v>
+      </c>
+      <c r="M70">
+        <v>0.7982656000000001</v>
+      </c>
+      <c r="N70">
+        <v>3.3817344</v>
+      </c>
+      <c r="O70">
+        <v>0.541077504</v>
+      </c>
+      <c r="P70">
+        <v>2.840656896</v>
+      </c>
+      <c r="Q70">
+        <v>4.720656895999999</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3885325383227302</v>
+      </c>
+      <c r="T70">
+        <v>3.602634681893042</v>
+      </c>
+      <c r="U70">
+        <v>0.055</v>
+      </c>
+      <c r="V70">
+        <v>0.16</v>
+      </c>
+      <c r="W70">
+        <v>0.0462</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>5.236352412029278</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.155619488722406</v>
+      </c>
+      <c r="C71">
+        <v>7.36087530177012</v>
+      </c>
+      <c r="D71">
+        <v>20.81823530177012</v>
+      </c>
+      <c r="E71">
+        <v>14.68336</v>
+      </c>
+      <c r="F71">
+        <v>14.72736</v>
+      </c>
+      <c r="G71">
+        <v>1.27</v>
+      </c>
+      <c r="H71">
+        <v>21.3</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>6.06</v>
+      </c>
+      <c r="K71">
+        <v>1.88</v>
+      </c>
+      <c r="L71">
+        <v>4.18</v>
+      </c>
+      <c r="M71">
+        <v>0.8100048000000002</v>
+      </c>
+      <c r="N71">
+        <v>3.3699952</v>
+      </c>
+      <c r="O71">
+        <v>0.5391992320000001</v>
+      </c>
+      <c r="P71">
+        <v>2.830795967999999</v>
+      </c>
+      <c r="Q71">
+        <v>4.710795967999999</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3991660926529227</v>
+      </c>
+      <c r="T71">
+        <v>3.712172135300921</v>
+      </c>
+      <c r="U71">
+        <v>0.055</v>
+      </c>
+      <c r="V71">
+        <v>0.16</v>
+      </c>
+      <c r="W71">
+        <v>0.0462</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>5.16046324663755</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1554925651815384</v>
+      </c>
+      <c r="C72">
+        <v>7.158618190575726</v>
+      </c>
+      <c r="D72">
+        <v>20.82941819057573</v>
+      </c>
+      <c r="E72">
+        <v>14.8968</v>
+      </c>
+      <c r="F72">
+        <v>14.9408</v>
+      </c>
+      <c r="G72">
+        <v>1.27</v>
+      </c>
+      <c r="H72">
+        <v>21.3</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>6.06</v>
+      </c>
+      <c r="K72">
+        <v>1.88</v>
+      </c>
+      <c r="L72">
+        <v>4.18</v>
+      </c>
+      <c r="M72">
+        <v>0.8217440000000001</v>
+      </c>
+      <c r="N72">
+        <v>3.358255999999999</v>
+      </c>
+      <c r="O72">
+        <v>0.5373209600000001</v>
+      </c>
+      <c r="P72">
+        <v>2.820935039999999</v>
+      </c>
+      <c r="Q72">
+        <v>4.700935039999999</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.410508550605128</v>
+      </c>
+      <c r="T72">
+        <v>3.829012085602659</v>
+      </c>
+      <c r="U72">
+        <v>0.055</v>
+      </c>
+      <c r="V72">
+        <v>0.16</v>
+      </c>
+      <c r="W72">
+        <v>0.0462</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>5.086742343114156</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1553656416406707</v>
+      </c>
+      <c r="C73">
+        <v>6.956373100017375</v>
+      </c>
+      <c r="D73">
+        <v>20.84061310001738</v>
+      </c>
+      <c r="E73">
+        <v>15.11024</v>
+      </c>
+      <c r="F73">
+        <v>15.15424</v>
+      </c>
+      <c r="G73">
+        <v>1.27</v>
+      </c>
+      <c r="H73">
+        <v>21.3</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>6.06</v>
+      </c>
+      <c r="K73">
+        <v>1.88</v>
+      </c>
+      <c r="L73">
+        <v>4.18</v>
+      </c>
+      <c r="M73">
+        <v>0.8334832</v>
+      </c>
+      <c r="N73">
+        <v>3.3465168</v>
+      </c>
+      <c r="O73">
+        <v>0.5354426880000001</v>
+      </c>
+      <c r="P73">
+        <v>2.811074112</v>
+      </c>
+      <c r="Q73">
+        <v>4.691074112</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.4226332470367956</v>
+      </c>
+      <c r="T73">
+        <v>3.953909963511412</v>
+      </c>
+      <c r="U73">
+        <v>0.055</v>
+      </c>
+      <c r="V73">
+        <v>0.16</v>
+      </c>
+      <c r="W73">
+        <v>0.0462</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>5.015098084760437</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1552387180998031</v>
+      </c>
+      <c r="C74">
+        <v>6.754140049487187</v>
+      </c>
+      <c r="D74">
+        <v>20.85182004948719</v>
+      </c>
+      <c r="E74">
+        <v>15.32368</v>
+      </c>
+      <c r="F74">
+        <v>15.36768</v>
+      </c>
+      <c r="G74">
+        <v>1.27</v>
+      </c>
+      <c r="H74">
+        <v>21.3</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>6.06</v>
+      </c>
+      <c r="K74">
+        <v>1.88</v>
+      </c>
+      <c r="L74">
+        <v>4.18</v>
+      </c>
+      <c r="M74">
+        <v>0.8452224</v>
+      </c>
+      <c r="N74">
+        <v>3.3347776</v>
+      </c>
+      <c r="O74">
+        <v>0.533564416</v>
+      </c>
+      <c r="P74">
+        <v>2.801213184</v>
+      </c>
+      <c r="Q74">
+        <v>4.681213184</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.4356239932135825</v>
+      </c>
+      <c r="T74">
+        <v>4.087729118413648</v>
+      </c>
+      <c r="U74">
+        <v>0.055</v>
+      </c>
+      <c r="V74">
+        <v>0.16</v>
+      </c>
+      <c r="W74">
+        <v>0.0462</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>4.945443944694319</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1551117945589355</v>
+      </c>
+      <c r="C75">
+        <v>6.551919058419047</v>
+      </c>
+      <c r="D75">
+        <v>20.86303905841905</v>
+      </c>
+      <c r="E75">
+        <v>15.53712</v>
+      </c>
+      <c r="F75">
+        <v>15.58112</v>
+      </c>
+      <c r="G75">
+        <v>1.27</v>
+      </c>
+      <c r="H75">
+        <v>21.3</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>6.06</v>
+      </c>
+      <c r="K75">
+        <v>1.88</v>
+      </c>
+      <c r="L75">
+        <v>4.18</v>
+      </c>
+      <c r="M75">
+        <v>0.8569616</v>
+      </c>
+      <c r="N75">
+        <v>3.3230384</v>
+      </c>
+      <c r="O75">
+        <v>0.531686144</v>
+      </c>
+      <c r="P75">
+        <v>2.791352256</v>
+      </c>
+      <c r="Q75">
+        <v>4.671352256</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.4495770168849462</v>
+      </c>
+      <c r="T75">
+        <v>4.231460803308643</v>
+      </c>
+      <c r="U75">
+        <v>0.055</v>
+      </c>
+      <c r="V75">
+        <v>0.16</v>
+      </c>
+      <c r="W75">
+        <v>0.0462</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>4.877698137232754</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1549848710180678</v>
+      </c>
+      <c r="C76">
+        <v>6.349710146288668</v>
+      </c>
+      <c r="D76">
+        <v>20.87427014628867</v>
+      </c>
+      <c r="E76">
+        <v>15.75056</v>
+      </c>
+      <c r="F76">
+        <v>15.79456</v>
+      </c>
+      <c r="G76">
+        <v>1.27</v>
+      </c>
+      <c r="H76">
+        <v>21.3</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>6.06</v>
+      </c>
+      <c r="K76">
+        <v>1.88</v>
+      </c>
+      <c r="L76">
+        <v>4.18</v>
+      </c>
+      <c r="M76">
+        <v>0.8687008000000001</v>
+      </c>
+      <c r="N76">
+        <v>3.3112992</v>
+      </c>
+      <c r="O76">
+        <v>0.529807872</v>
+      </c>
+      <c r="P76">
+        <v>2.781491328</v>
+      </c>
+      <c r="Q76">
+        <v>4.661491327999999</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.4646033500694916</v>
+      </c>
+      <c r="T76">
+        <v>4.386248771657098</v>
+      </c>
+      <c r="U76">
+        <v>0.055</v>
+      </c>
+      <c r="V76">
+        <v>0.16</v>
+      </c>
+      <c r="W76">
+        <v>0.0462</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>4.811783297540418</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1548579474772002</v>
+      </c>
+      <c r="C77">
+        <v>6.147513332613723</v>
+      </c>
+      <c r="D77">
+        <v>20.88551333261373</v>
+      </c>
+      <c r="E77">
+        <v>15.964</v>
+      </c>
+      <c r="F77">
+        <v>16.008</v>
+      </c>
+      <c r="G77">
+        <v>1.27</v>
+      </c>
+      <c r="H77">
+        <v>21.3</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>6.06</v>
+      </c>
+      <c r="K77">
+        <v>1.88</v>
+      </c>
+      <c r="L77">
+        <v>4.18</v>
+      </c>
+      <c r="M77">
+        <v>0.8804400000000001</v>
+      </c>
+      <c r="N77">
+        <v>3.29956</v>
+      </c>
+      <c r="O77">
+        <v>0.5279296</v>
+      </c>
+      <c r="P77">
+        <v>2.771630399999999</v>
+      </c>
+      <c r="Q77">
+        <v>4.651630399999999</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.4808317899088008</v>
+      </c>
+      <c r="T77">
+        <v>4.553419777473431</v>
+      </c>
+      <c r="U77">
+        <v>0.055</v>
+      </c>
+      <c r="V77">
+        <v>0.16</v>
+      </c>
+      <c r="W77">
+        <v>0.0462</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>4.747626186906546</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1547310239363325</v>
+      </c>
+      <c r="C78">
+        <v>5.94532863695396</v>
+      </c>
+      <c r="D78">
+        <v>20.89676863695396</v>
+      </c>
+      <c r="E78">
+        <v>16.17744</v>
+      </c>
+      <c r="F78">
+        <v>16.22144</v>
+      </c>
+      <c r="G78">
+        <v>1.27</v>
+      </c>
+      <c r="H78">
+        <v>21.3</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>6.06</v>
+      </c>
+      <c r="K78">
+        <v>1.88</v>
+      </c>
+      <c r="L78">
+        <v>4.18</v>
+      </c>
+      <c r="M78">
+        <v>0.8921792000000001</v>
+      </c>
+      <c r="N78">
+        <v>3.2878208</v>
+      </c>
+      <c r="O78">
+        <v>0.526051328</v>
+      </c>
+      <c r="P78">
+        <v>2.761769472</v>
+      </c>
+      <c r="Q78">
+        <v>4.641769472</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.498412599734719</v>
+      </c>
+      <c r="T78">
+        <v>4.734521700441125</v>
+      </c>
+      <c r="U78">
+        <v>0.055</v>
+      </c>
+      <c r="V78">
+        <v>0.16</v>
+      </c>
+      <c r="W78">
+        <v>0.0462</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>4.685157421289355</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1546041003954649</v>
+      </c>
+      <c r="C79">
+        <v>5.743156078911319</v>
+      </c>
+      <c r="D79">
+        <v>20.90803607891132</v>
+      </c>
+      <c r="E79">
+        <v>16.39088</v>
+      </c>
+      <c r="F79">
+        <v>16.43488</v>
+      </c>
+      <c r="G79">
+        <v>1.27</v>
+      </c>
+      <c r="H79">
+        <v>21.3</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>6.06</v>
+      </c>
+      <c r="K79">
+        <v>1.88</v>
+      </c>
+      <c r="L79">
+        <v>4.18</v>
+      </c>
+      <c r="M79">
+        <v>0.9039184</v>
+      </c>
+      <c r="N79">
+        <v>3.276081599999999</v>
+      </c>
+      <c r="O79">
+        <v>0.524173056</v>
+      </c>
+      <c r="P79">
+        <v>2.751908544</v>
+      </c>
+      <c r="Q79">
+        <v>4.631908544</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.5175221756324562</v>
+      </c>
+      <c r="T79">
+        <v>4.931371616710356</v>
+      </c>
+      <c r="U79">
+        <v>0.055</v>
+      </c>
+      <c r="V79">
+        <v>0.16</v>
+      </c>
+      <c r="W79">
+        <v>0.0462</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>4.624311221012869</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1544771768545973</v>
+      </c>
+      <c r="C80">
+        <v>5.540995678130024</v>
+      </c>
+      <c r="D80">
+        <v>20.91931567813003</v>
+      </c>
+      <c r="E80">
+        <v>16.60432</v>
+      </c>
+      <c r="F80">
+        <v>16.64832</v>
+      </c>
+      <c r="G80">
+        <v>1.27</v>
+      </c>
+      <c r="H80">
+        <v>21.3</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>6.06</v>
+      </c>
+      <c r="K80">
+        <v>1.88</v>
+      </c>
+      <c r="L80">
+        <v>4.18</v>
+      </c>
+      <c r="M80">
+        <v>0.9156576000000001</v>
+      </c>
+      <c r="N80">
+        <v>3.264342399999999</v>
+      </c>
+      <c r="O80">
+        <v>0.522294784</v>
+      </c>
+      <c r="P80">
+        <v>2.742047615999999</v>
+      </c>
+      <c r="Q80">
+        <v>4.622047616</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.538368985702715</v>
+      </c>
+      <c r="T80">
+        <v>5.146116979913155</v>
+      </c>
+      <c r="U80">
+        <v>0.055</v>
+      </c>
+      <c r="V80">
+        <v>0.16</v>
+      </c>
+      <c r="W80">
+        <v>0.0462</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>4.565025179717832</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1543502533137296</v>
+      </c>
+      <c r="C81">
+        <v>5.33884745429674</v>
+      </c>
+      <c r="D81">
+        <v>20.93060745429674</v>
+      </c>
+      <c r="E81">
+        <v>16.81776</v>
+      </c>
+      <c r="F81">
+        <v>16.86176</v>
+      </c>
+      <c r="G81">
+        <v>1.27</v>
+      </c>
+      <c r="H81">
+        <v>21.3</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>6.06</v>
+      </c>
+      <c r="K81">
+        <v>1.88</v>
+      </c>
+      <c r="L81">
+        <v>4.18</v>
+      </c>
+      <c r="M81">
+        <v>0.9273968</v>
+      </c>
+      <c r="N81">
+        <v>3.2526032</v>
+      </c>
+      <c r="O81">
+        <v>0.5204165120000001</v>
+      </c>
+      <c r="P81">
+        <v>2.732186688</v>
+      </c>
+      <c r="Q81">
+        <v>4.612186688</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.5612012062558556</v>
+      </c>
+      <c r="T81">
+        <v>5.381314282468601</v>
+      </c>
+      <c r="U81">
+        <v>0.055</v>
+      </c>
+      <c r="V81">
+        <v>0.16</v>
+      </c>
+      <c r="W81">
+        <v>0.0462</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>4.507240050860645</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.156776929772862</v>
+      </c>
+      <c r="C82">
+        <v>4.911607642576538</v>
+      </c>
+      <c r="D82">
+        <v>20.71680764257654</v>
+      </c>
+      <c r="E82">
+        <v>17.0312</v>
+      </c>
+      <c r="F82">
+        <v>17.0752</v>
+      </c>
+      <c r="G82">
+        <v>1.27</v>
+      </c>
+      <c r="H82">
+        <v>21.3</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>6.06</v>
+      </c>
+      <c r="K82">
+        <v>1.88</v>
+      </c>
+      <c r="L82">
+        <v>4.18</v>
+      </c>
+      <c r="M82">
+        <v>1.00402176</v>
+      </c>
+      <c r="N82">
+        <v>3.175978239999999</v>
+      </c>
+      <c r="O82">
+        <v>0.5081565184</v>
+      </c>
+      <c r="P82">
+        <v>2.667821721599999</v>
+      </c>
+      <c r="Q82">
+        <v>4.547821721599999</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.5863166488643101</v>
+      </c>
+      <c r="T82">
+        <v>5.640031315279592</v>
+      </c>
+      <c r="U82">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V82">
+        <v>0.16</v>
+      </c>
+      <c r="W82">
+        <v>0.04939200000000001</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>4.163256382013073</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1566819262319944</v>
+      </c>
+      <c r="C83">
+        <v>4.706455646427354</v>
+      </c>
+      <c r="D83">
+        <v>20.72509564642736</v>
+      </c>
+      <c r="E83">
+        <v>17.24464</v>
+      </c>
+      <c r="F83">
+        <v>17.28864</v>
+      </c>
+      <c r="G83">
+        <v>1.27</v>
+      </c>
+      <c r="H83">
+        <v>21.3</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>6.06</v>
+      </c>
+      <c r="K83">
+        <v>1.88</v>
+      </c>
+      <c r="L83">
+        <v>4.18</v>
+      </c>
+      <c r="M83">
+        <v>1.016572032</v>
+      </c>
+      <c r="N83">
+        <v>3.163427968</v>
+      </c>
+      <c r="O83">
+        <v>0.50614847488</v>
+      </c>
+      <c r="P83">
+        <v>2.65727949312</v>
+      </c>
+      <c r="Q83">
+        <v>4.53727949312</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.6140758222736549</v>
+      </c>
+      <c r="T83">
+        <v>5.925981719965424</v>
+      </c>
+      <c r="U83">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V83">
+        <v>0.16</v>
+      </c>
+      <c r="W83">
+        <v>0.04939200000000001</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>4.111858155074641</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1565869226911267</v>
+      </c>
+      <c r="C84">
+        <v>4.501310284360088</v>
+      </c>
+      <c r="D84">
+        <v>20.73339028436009</v>
+      </c>
+      <c r="E84">
+        <v>17.45808</v>
+      </c>
+      <c r="F84">
+        <v>17.50208</v>
+      </c>
+      <c r="G84">
+        <v>1.27</v>
+      </c>
+      <c r="H84">
+        <v>21.3</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>6.06</v>
+      </c>
+      <c r="K84">
+        <v>1.88</v>
+      </c>
+      <c r="L84">
+        <v>4.18</v>
+      </c>
+      <c r="M84">
+        <v>1.029122304</v>
+      </c>
+      <c r="N84">
+        <v>3.150877695999999</v>
+      </c>
+      <c r="O84">
+        <v>0.50414043136</v>
+      </c>
+      <c r="P84">
+        <v>2.64673726464</v>
+      </c>
+      <c r="Q84">
+        <v>4.526737264639999</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.6449193482840376</v>
+      </c>
+      <c r="T84">
+        <v>6.243704391838571</v>
+      </c>
+      <c r="U84">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V84">
+        <v>0.16</v>
+      </c>
+      <c r="W84">
+        <v>0.04939200000000001</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>4.061713543427389</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1564919191502591</v>
+      </c>
+      <c r="C85">
+        <v>4.296171564343243</v>
+      </c>
+      <c r="D85">
+        <v>20.74169156434325</v>
+      </c>
+      <c r="E85">
+        <v>17.67152</v>
+      </c>
+      <c r="F85">
+        <v>17.71552</v>
+      </c>
+      <c r="G85">
+        <v>1.27</v>
+      </c>
+      <c r="H85">
+        <v>21.3</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>6.06</v>
+      </c>
+      <c r="K85">
+        <v>1.88</v>
+      </c>
+      <c r="L85">
+        <v>4.18</v>
+      </c>
+      <c r="M85">
+        <v>1.041672576</v>
+      </c>
+      <c r="N85">
+        <v>3.138327424</v>
+      </c>
+      <c r="O85">
+        <v>0.50213238784</v>
+      </c>
+      <c r="P85">
+        <v>2.63619503616</v>
+      </c>
+      <c r="Q85">
+        <v>4.516195036159999</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.6793915244132891</v>
+      </c>
+      <c r="T85">
+        <v>6.598806201579146</v>
+      </c>
+      <c r="U85">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V85">
+        <v>0.16</v>
+      </c>
+      <c r="W85">
+        <v>0.04939200000000001</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>4.012777235675253</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1593604356093914</v>
+      </c>
+      <c r="C86">
+        <v>3.834979240198798</v>
+      </c>
+      <c r="D86">
+        <v>20.4939392401988</v>
+      </c>
+      <c r="E86">
+        <v>17.88496</v>
+      </c>
+      <c r="F86">
+        <v>17.92896</v>
+      </c>
+      <c r="G86">
+        <v>1.27</v>
+      </c>
+      <c r="H86">
+        <v>21.3</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>6.06</v>
+      </c>
+      <c r="K86">
+        <v>1.88</v>
+      </c>
+      <c r="L86">
+        <v>4.18</v>
+      </c>
+      <c r="M86">
+        <v>1.12952448</v>
+      </c>
+      <c r="N86">
+        <v>3.05047552</v>
+      </c>
+      <c r="O86">
+        <v>0.4880760832000001</v>
+      </c>
+      <c r="P86">
+        <v>2.5623994368</v>
+      </c>
+      <c r="Q86">
+        <v>4.4423994368</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.7181727225586965</v>
+      </c>
+      <c r="T86">
+        <v>6.99829573753729</v>
+      </c>
+      <c r="U86">
+        <v>0.063</v>
+      </c>
+      <c r="V86">
+        <v>0.16</v>
+      </c>
+      <c r="W86">
+        <v>0.05292</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>3.700672339567178</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1593007120685238</v>
+      </c>
+      <c r="C87">
+        <v>3.626637186195612</v>
+      </c>
+      <c r="D87">
+        <v>20.49903718619561</v>
+      </c>
+      <c r="E87">
+        <v>18.0984</v>
+      </c>
+      <c r="F87">
+        <v>18.1424</v>
+      </c>
+      <c r="G87">
+        <v>1.27</v>
+      </c>
+      <c r="H87">
+        <v>21.3</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>6.06</v>
+      </c>
+      <c r="K87">
+        <v>1.88</v>
+      </c>
+      <c r="L87">
+        <v>4.18</v>
+      </c>
+      <c r="M87">
+        <v>1.1429712</v>
+      </c>
+      <c r="N87">
+        <v>3.0370288</v>
+      </c>
+      <c r="O87">
+        <v>0.4859246080000001</v>
+      </c>
+      <c r="P87">
+        <v>2.551104192</v>
+      </c>
+      <c r="Q87">
+        <v>4.431104191999999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.762124747123492</v>
+      </c>
+      <c r="T87">
+        <v>7.451050544956522</v>
+      </c>
+      <c r="U87">
+        <v>0.063</v>
+      </c>
+      <c r="V87">
+        <v>0.16</v>
+      </c>
+      <c r="W87">
+        <v>0.05292</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>3.657135017925211</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1592409885276562</v>
+      </c>
+      <c r="C88">
+        <v>3.418297669090737</v>
+      </c>
+      <c r="D88">
+        <v>20.50413766909074</v>
+      </c>
+      <c r="E88">
+        <v>18.31184</v>
+      </c>
+      <c r="F88">
+        <v>18.35584</v>
+      </c>
+      <c r="G88">
+        <v>1.27</v>
+      </c>
+      <c r="H88">
+        <v>21.3</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>6.06</v>
+      </c>
+      <c r="K88">
+        <v>1.88</v>
+      </c>
+      <c r="L88">
+        <v>4.18</v>
+      </c>
+      <c r="M88">
+        <v>1.15641792</v>
+      </c>
+      <c r="N88">
+        <v>3.02358208</v>
+      </c>
+      <c r="O88">
+        <v>0.4837731328000001</v>
+      </c>
+      <c r="P88">
+        <v>2.5398089472</v>
+      </c>
+      <c r="Q88">
+        <v>4.4198089472</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.8123556323404013</v>
+      </c>
+      <c r="T88">
+        <v>7.968484610578503</v>
+      </c>
+      <c r="U88">
+        <v>0.063</v>
+      </c>
+      <c r="V88">
+        <v>0.16</v>
+      </c>
+      <c r="W88">
+        <v>0.05292</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>3.614610192135383</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1591812649867886</v>
+      </c>
+      <c r="C89">
+        <v>3.209960690778303</v>
+      </c>
+      <c r="D89">
+        <v>20.50924069077831</v>
+      </c>
+      <c r="E89">
+        <v>18.52528</v>
+      </c>
+      <c r="F89">
+        <v>18.56928</v>
+      </c>
+      <c r="G89">
+        <v>1.27</v>
+      </c>
+      <c r="H89">
+        <v>21.3</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>6.06</v>
+      </c>
+      <c r="K89">
+        <v>1.88</v>
+      </c>
+      <c r="L89">
+        <v>4.18</v>
+      </c>
+      <c r="M89">
+        <v>1.16986464</v>
+      </c>
+      <c r="N89">
+        <v>3.01013536</v>
+      </c>
+      <c r="O89">
+        <v>0.4816216576</v>
+      </c>
+      <c r="P89">
+        <v>2.5285137024</v>
+      </c>
+      <c r="Q89">
+        <v>4.4085137024</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.8703143460522196</v>
+      </c>
+      <c r="T89">
+        <v>8.565523917065406</v>
+      </c>
+      <c r="U89">
+        <v>0.063</v>
+      </c>
+      <c r="V89">
+        <v>0.16</v>
+      </c>
+      <c r="W89">
+        <v>0.05292</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>3.573062948547619</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1591215414459209</v>
+      </c>
+      <c r="C90">
+        <v>3.001626253154324</v>
+      </c>
+      <c r="D90">
+        <v>20.51434625315433</v>
+      </c>
+      <c r="E90">
+        <v>18.73872</v>
+      </c>
+      <c r="F90">
+        <v>18.78272</v>
+      </c>
+      <c r="G90">
+        <v>1.27</v>
+      </c>
+      <c r="H90">
+        <v>21.3</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>6.06</v>
+      </c>
+      <c r="K90">
+        <v>1.88</v>
+      </c>
+      <c r="L90">
+        <v>4.18</v>
+      </c>
+      <c r="M90">
+        <v>1.18331136</v>
+      </c>
+      <c r="N90">
+        <v>2.996688639999999</v>
+      </c>
+      <c r="O90">
+        <v>0.4794701824</v>
+      </c>
+      <c r="P90">
+        <v>2.517218457599999</v>
+      </c>
+      <c r="Q90">
+        <v>4.397218457599999</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.9379328453826743</v>
+      </c>
+      <c r="T90">
+        <v>9.262069774633456</v>
+      </c>
+      <c r="U90">
+        <v>0.063</v>
+      </c>
+      <c r="V90">
+        <v>0.16</v>
+      </c>
+      <c r="W90">
+        <v>0.05292</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>3.532459960495942</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1643697779050533</v>
+      </c>
+      <c r="C91">
+        <v>2.349027581879291</v>
+      </c>
+      <c r="D91">
+        <v>20.07518758187929</v>
+      </c>
+      <c r="E91">
+        <v>18.95216</v>
+      </c>
+      <c r="F91">
+        <v>18.99616</v>
+      </c>
+      <c r="G91">
+        <v>1.27</v>
+      </c>
+      <c r="H91">
+        <v>21.3</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>6.06</v>
+      </c>
+      <c r="K91">
+        <v>1.88</v>
+      </c>
+      <c r="L91">
+        <v>4.18</v>
+      </c>
+      <c r="M91">
+        <v>1.331630816</v>
+      </c>
+      <c r="N91">
+        <v>2.848369184</v>
+      </c>
+      <c r="O91">
+        <v>0.4557390694400001</v>
+      </c>
+      <c r="P91">
+        <v>2.39263011456</v>
+      </c>
+      <c r="Q91">
+        <v>4.27263011456</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.017845617318666</v>
+      </c>
+      <c r="T91">
+        <v>10.08526033357752</v>
+      </c>
+      <c r="U91">
+        <v>0.0701</v>
+      </c>
+      <c r="V91">
+        <v>0.16</v>
+      </c>
+      <c r="W91">
+        <v>0.05888399999999999</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>3.139008161853774</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1643696943641856</v>
+      </c>
+      <c r="C92">
+        <v>2.135594422714494</v>
+      </c>
+      <c r="D92">
+        <v>20.0751944227145</v>
+      </c>
+      <c r="E92">
+        <v>19.1656</v>
+      </c>
+      <c r="F92">
+        <v>19.2096</v>
+      </c>
+      <c r="G92">
+        <v>1.27</v>
+      </c>
+      <c r="H92">
+        <v>21.3</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>6.06</v>
+      </c>
+      <c r="K92">
+        <v>1.88</v>
+      </c>
+      <c r="L92">
+        <v>4.18</v>
+      </c>
+      <c r="M92">
+        <v>1.34659296</v>
+      </c>
+      <c r="N92">
+        <v>2.83340704</v>
+      </c>
+      <c r="O92">
+        <v>0.4533451264000001</v>
+      </c>
+      <c r="P92">
+        <v>2.3800619136</v>
+      </c>
+      <c r="Q92">
+        <v>4.2600619136</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.113740943641857</v>
+      </c>
+      <c r="T92">
+        <v>11.07308900431039</v>
+      </c>
+      <c r="U92">
+        <v>0.0701</v>
+      </c>
+      <c r="V92">
+        <v>0.16</v>
+      </c>
+      <c r="W92">
+        <v>0.05888399999999999</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>3.104130293388731</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.164369610823318</v>
+      </c>
+      <c r="C93">
+        <v>1.922161263554361</v>
+      </c>
+      <c r="D93">
+        <v>20.07520126355436</v>
+      </c>
+      <c r="E93">
+        <v>19.37904</v>
+      </c>
+      <c r="F93">
+        <v>19.42304</v>
+      </c>
+      <c r="G93">
+        <v>1.27</v>
+      </c>
+      <c r="H93">
+        <v>21.3</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>6.06</v>
+      </c>
+      <c r="K93">
+        <v>1.88</v>
+      </c>
+      <c r="L93">
+        <v>4.18</v>
+      </c>
+      <c r="M93">
+        <v>1.361555104</v>
+      </c>
+      <c r="N93">
+        <v>2.818444896</v>
+      </c>
+      <c r="O93">
+        <v>0.4509511833600001</v>
+      </c>
+      <c r="P93">
+        <v>2.36749371264</v>
+      </c>
+      <c r="Q93">
+        <v>4.24749371264</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.230946342481311</v>
+      </c>
+      <c r="T93">
+        <v>12.28043515742835</v>
+      </c>
+      <c r="U93">
+        <v>0.0701</v>
+      </c>
+      <c r="V93">
+        <v>0.16</v>
+      </c>
+      <c r="W93">
+        <v>0.05888399999999999</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>3.070018971483361</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1643695272824504</v>
+      </c>
+      <c r="C94">
+        <v>1.708728104398887</v>
+      </c>
+      <c r="D94">
+        <v>20.07520810439889</v>
+      </c>
+      <c r="E94">
+        <v>19.59248</v>
+      </c>
+      <c r="F94">
+        <v>19.63648</v>
+      </c>
+      <c r="G94">
+        <v>1.27</v>
+      </c>
+      <c r="H94">
+        <v>21.3</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>6.06</v>
+      </c>
+      <c r="K94">
+        <v>1.88</v>
+      </c>
+      <c r="L94">
+        <v>4.18</v>
+      </c>
+      <c r="M94">
+        <v>1.376517248</v>
+      </c>
+      <c r="N94">
+        <v>2.803482752</v>
+      </c>
+      <c r="O94">
+        <v>0.4485572403200001</v>
+      </c>
+      <c r="P94">
+        <v>2.35492551168</v>
+      </c>
+      <c r="Q94">
+        <v>4.23492551168</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.37745309103063</v>
+      </c>
+      <c r="T94">
+        <v>13.7896178488258</v>
+      </c>
+      <c r="U94">
+        <v>0.0701</v>
+      </c>
+      <c r="V94">
+        <v>0.16</v>
+      </c>
+      <c r="W94">
+        <v>0.05888399999999999</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>3.036649200054193</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1643694437415827</v>
+      </c>
+      <c r="C95">
+        <v>1.49529494524808</v>
+      </c>
+      <c r="D95">
+        <v>20.07521494524808</v>
+      </c>
+      <c r="E95">
+        <v>19.80592</v>
+      </c>
+      <c r="F95">
+        <v>19.84992</v>
+      </c>
+      <c r="G95">
+        <v>1.27</v>
+      </c>
+      <c r="H95">
+        <v>21.3</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>6.06</v>
+      </c>
+      <c r="K95">
+        <v>1.88</v>
+      </c>
+      <c r="L95">
+        <v>4.18</v>
+      </c>
+      <c r="M95">
+        <v>1.391479392</v>
+      </c>
+      <c r="N95">
+        <v>2.788520608</v>
+      </c>
+      <c r="O95">
+        <v>0.44616329728</v>
+      </c>
+      <c r="P95">
+        <v>2.34235731072</v>
+      </c>
+      <c r="Q95">
+        <v>4.22235731072</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.56581891059404</v>
+      </c>
+      <c r="T95">
+        <v>15.72999559490823</v>
+      </c>
+      <c r="U95">
+        <v>0.0701</v>
+      </c>
+      <c r="V95">
+        <v>0.16</v>
+      </c>
+      <c r="W95">
+        <v>0.05888399999999999</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>3.003997058118127</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1811878402007151</v>
+      </c>
+      <c r="C96">
+        <v>-0.006928247989502978</v>
+      </c>
+      <c r="D96">
+        <v>18.7864317520105</v>
+      </c>
+      <c r="E96">
+        <v>20.01936</v>
+      </c>
+      <c r="F96">
+        <v>20.06336</v>
+      </c>
+      <c r="G96">
+        <v>1.27</v>
+      </c>
+      <c r="H96">
+        <v>21.3</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>6.06</v>
+      </c>
+      <c r="K96">
+        <v>1.88</v>
+      </c>
+      <c r="L96">
+        <v>4.18</v>
+      </c>
+      <c r="M96">
+        <v>1.833791104000001</v>
+      </c>
+      <c r="N96">
+        <v>2.346208895999999</v>
+      </c>
+      <c r="O96">
+        <v>0.37539342336</v>
+      </c>
+      <c r="P96">
+        <v>1.970815472639999</v>
+      </c>
+      <c r="Q96">
+        <v>3.850815472639999</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.816973336678587</v>
+      </c>
+      <c r="T96">
+        <v>18.31716592301814</v>
+      </c>
+      <c r="U96">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V96">
+        <v>0.16</v>
+      </c>
+      <c r="W96">
+        <v>0.07677600000000001</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>2.27943084186758</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1813666766598475</v>
+      </c>
+      <c r="C97">
+        <v>-0.2331838517274036</v>
+      </c>
+      <c r="D97">
+        <v>18.7736161482726</v>
+      </c>
+      <c r="E97">
+        <v>20.2328</v>
+      </c>
+      <c r="F97">
+        <v>20.2768</v>
+      </c>
+      <c r="G97">
+        <v>1.27</v>
+      </c>
+      <c r="H97">
+        <v>21.3</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>6.06</v>
+      </c>
+      <c r="K97">
+        <v>1.88</v>
+      </c>
+      <c r="L97">
+        <v>4.18</v>
+      </c>
+      <c r="M97">
+        <v>1.85329952</v>
+      </c>
+      <c r="N97">
+        <v>2.32670048</v>
+      </c>
+      <c r="O97">
+        <v>0.3722720768</v>
+      </c>
+      <c r="P97">
+        <v>1.954428403199999</v>
+      </c>
+      <c r="Q97">
+        <v>3.8344284032</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.168589533196952</v>
+      </c>
+      <c r="T97">
+        <v>21.93920438237202</v>
+      </c>
+      <c r="U97">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V97">
+        <v>0.16</v>
+      </c>
+      <c r="W97">
+        <v>0.07677600000000001</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>2.255436833005816</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1815455131189798</v>
+      </c>
+      <c r="C98">
+        <v>-0.4594219824573571</v>
+      </c>
+      <c r="D98">
+        <v>18.76081801754264</v>
+      </c>
+      <c r="E98">
+        <v>20.44624</v>
+      </c>
+      <c r="F98">
+        <v>20.49024</v>
+      </c>
+      <c r="G98">
+        <v>1.27</v>
+      </c>
+      <c r="H98">
+        <v>21.3</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>6.06</v>
+      </c>
+      <c r="K98">
+        <v>1.88</v>
+      </c>
+      <c r="L98">
+        <v>4.18</v>
+      </c>
+      <c r="M98">
+        <v>1.872807936</v>
+      </c>
+      <c r="N98">
+        <v>2.307192064</v>
+      </c>
+      <c r="O98">
+        <v>0.36915073024</v>
+      </c>
+      <c r="P98">
+        <v>1.93804133376</v>
+      </c>
+      <c r="Q98">
+        <v>3.81804133376</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.696013827974493</v>
+      </c>
+      <c r="T98">
+        <v>27.37226207140276</v>
+      </c>
+      <c r="U98">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V98">
+        <v>0.16</v>
+      </c>
+      <c r="W98">
+        <v>0.07677600000000001</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>2.231942699328672</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.1817243495781122</v>
+      </c>
+      <c r="C99">
+        <v>-0.6856426758895182</v>
+      </c>
+      <c r="D99">
+        <v>18.74803732411048</v>
+      </c>
+      <c r="E99">
+        <v>20.65968</v>
+      </c>
+      <c r="F99">
+        <v>20.70368</v>
+      </c>
+      <c r="G99">
+        <v>1.27</v>
+      </c>
+      <c r="H99">
+        <v>21.3</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>6.06</v>
+      </c>
+      <c r="K99">
+        <v>1.88</v>
+      </c>
+      <c r="L99">
+        <v>4.18</v>
+      </c>
+      <c r="M99">
+        <v>1.892316352</v>
+      </c>
+      <c r="N99">
+        <v>2.287683647999999</v>
+      </c>
+      <c r="O99">
+        <v>0.36602938368</v>
+      </c>
+      <c r="P99">
+        <v>1.921654264319999</v>
+      </c>
+      <c r="Q99">
+        <v>3.801654264319999</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.575054319270404</v>
+      </c>
+      <c r="T99">
+        <v>36.42735821978742</v>
+      </c>
+      <c r="U99">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V99">
+        <v>0.16</v>
+      </c>
+      <c r="W99">
+        <v>0.07677600000000001</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>2.208932980778892</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1819031860372446</v>
+      </c>
+      <c r="C100">
+        <v>-0.9118459676367721</v>
+      </c>
+      <c r="D100">
+        <v>18.73527403236323</v>
+      </c>
+      <c r="E100">
+        <v>20.87312</v>
+      </c>
+      <c r="F100">
+        <v>20.91712</v>
+      </c>
+      <c r="G100">
+        <v>1.27</v>
+      </c>
+      <c r="H100">
+        <v>21.3</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>6.06</v>
+      </c>
+      <c r="K100">
+        <v>1.88</v>
+      </c>
+      <c r="L100">
+        <v>4.18</v>
+      </c>
+      <c r="M100">
+        <v>1.911824768</v>
+      </c>
+      <c r="N100">
+        <v>2.268175231999999</v>
+      </c>
+      <c r="O100">
+        <v>0.36290803712</v>
+      </c>
+      <c r="P100">
+        <v>1.90526719488</v>
+      </c>
+      <c r="Q100">
+        <v>3.785267194879999</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>5.333135301862223</v>
+      </c>
+      <c r="T100">
+        <v>54.53755051655673</v>
+      </c>
+      <c r="U100">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V100">
+        <v>0.16</v>
+      </c>
+      <c r="W100">
+        <v>0.07677600000000001</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>2.186392848321964</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.1820820224963769</v>
+      </c>
+      <c r="C101">
+        <v>-1.138031893215118</v>
+      </c>
+      <c r="D101">
+        <v>18.72252810678489</v>
+      </c>
+      <c r="E101">
+        <v>21.08656</v>
+      </c>
+      <c r="F101">
+        <v>21.13056</v>
+      </c>
+      <c r="G101">
+        <v>1.27</v>
+      </c>
+      <c r="H101">
+        <v>21.3</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>6.06</v>
+      </c>
+      <c r="K101">
+        <v>1.88</v>
+      </c>
+      <c r="L101">
+        <v>4.18</v>
+      </c>
+      <c r="M101">
+        <v>1.931333184000001</v>
+      </c>
+      <c r="N101">
+        <v>2.248666815999999</v>
+      </c>
+      <c r="O101">
+        <v>0.35978669056</v>
+      </c>
+      <c r="P101">
+        <v>1.888880125439999</v>
+      </c>
+      <c r="Q101">
+        <v>3.768880125439999</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>10.60737824963768</v>
+      </c>
+      <c r="T101">
+        <v>108.8681274068647</v>
+      </c>
+      <c r="U101">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V101">
+        <v>0.16</v>
+      </c>
+      <c r="W101">
+        <v>0.07677600000000001</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>2.164308072076288</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
